--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -19,11 +19,2045 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="770">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="794">
+  <x:si>
+    <x:t>햄스터들의 사생활을 존중하는 작은 방</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Tower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Carousel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스트레스를 해소시켜주는 미끄럼틀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미끄럼틀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Wheel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Minihome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_PC_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Tower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨갛게 달아오른 불씨가 포근한 온기를 전해주는 화로 난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Toy_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Audio_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Synthesizer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반달 모양의 등받이가 포인트인 아담하고 귀여운 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초록빛 쿠션과 주황색 프레임이 어우러진 포근한 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>팽이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다트판</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸랑이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대부분의 햄스터들이 좋아하는 회전목마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Wheel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Pouf_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Dumbbell_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본적인 디자인의 묵직한 덤벨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Dumbbell_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혼자 쉬기 딱 좋은 아늑한 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Toilet_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Computer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전국 모든 딸들이 탐내는 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Pouf_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Keyboard_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Treadmill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밝은 핑크색이 돋보이는 가벼운 덤벨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Pouf_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_GameConsole_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Pouf_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_GameConsole_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Pouf_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Pouf_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_GameConsole_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Synthesizer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Toilet_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Toilet_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자연의 색감을 담은 편안한 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>넓고 튼튼한 프레임의 포근한 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작지만 존재감 있는 초록 친구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Bed_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Pouf_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따뜻한 분위기가 느껴지는 원목 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Toilet_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달려라 쳇바퀴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Toy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Toilet_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_TV_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따스한 황혼빛 색감과 기하학 무늬가 어우러진 포근한 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Pouf_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짙은 원목 프레임이 편안하고 아늑한 느낌을 주는 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>톡톡 튀는 색감과 레트로한 감성이 매력적인 카세트 라디오</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Piano_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동글동글 폭신한 쿠션에 앉아 편안하게 쉬기 좋은 푸프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산뜻한 민트빛 원형 무늬가 포인트가 되는 포근한 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신나는 음악으로 햄찌의 하루를 즐겁게 채워주는 스피커</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싱그러운 색감으로 공간에 생기를 더해주는 산뜻한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Toilet_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Pouf_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Toilet_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우아한 기둥 장식이 돋보이는 고급스러운 분위기의 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선명한 레드 쿠션과 메탈 프레임이 어우러진 깔끔한 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동글동글한 좌판과 세 개의 다리가 어우러진 아담한 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Toilet_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따스한 모랫빛과 짙은 푸른빛이 어우러진 멋스러운 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_TV_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_TV_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Treadmill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은은한 보랏빛이 공간을 포근하게 채워주는 1인용 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Pouf_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Pouf_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블록처럼 단순하고 통통한 모양이 매력적인 작은 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흔들면 재미있는 소리가 날 것 같은 알록달록한 딸랑이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>편하게 기대어 느긋한 시간을 보내기 좋은 나무 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Pouf_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동글동글한 좌판과 통통한 다리가 귀여운 포인트 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_TV_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둥근 좌판과 부드럽게 휘어진 다리가 어우러진 산뜻한 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Toy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_TV_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둥근 장식 프레임과 짙은 초록빛이 어우러진 클래식한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화사한 벚꽃빛 침구가 포근한 분위기를 더해주는 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싱그러운 색감과 둥근 등받이가 어우러진 포근한 안락의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>톡톡 튀는 베리 컬러와 둥근 프레임이 매력적인 높은 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>푹신한 쿠션과 깔끔한 디자인이 돋보이는 파란색 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>꽃잎처럼 포근하게 감싸주는 사랑스러운 분홍빛 1인용 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭신한 둥근 좌판과 따뜻한 우드톤이 어우러진 아담한 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따스한 가을 들판을 닮은 색감이 아늑함을 더해주는 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따뜻한 선율로 햄찌의 하루를 감성 가득 채워주는 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Audio_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따스한 모래빛과 시원한 바다빛이 어우러진 포근한 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Audio_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_TV_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Toy_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/BarbellStand_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Audio_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Audio_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Audio_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잔잔한 음악과 함께 느긋한 시간을 보낼 수 있는 라디오</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Darts_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스탠드에 올려 더욱 편하게 연주할 수 있는 신디사이저</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풍성한 사운드로 햄찌의 공간을 가득 채워주는 스테레오</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/GameConsole_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Audio_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Ball_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Mouse_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/ExerciseBike_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신나는 음악에 맞춰 절로 몸이 들썩이는 알록달록 붐박스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Audio_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빙글빙글 돌리며 가지고 놀 수 있는 알록달록한 팽이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/GameConsole_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Toy_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Pouf_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Pouf_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공주들은 작은 침대는 사치라는 것을 깨닫게 해주는 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따스한 호박빛 색감이 아늑한 분위기를 더해주는 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_TV_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/GameConsole_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Toy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회전목마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상큼한 청록빛 프레임과 달콤한 핑크빛 쿠션이 톡톡 튀는 분위기를 더해주는 1인용 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>깊은 브라운빛 쿠션과 겹겹이 나뉜 등받이가 편안함을 더해주는 클래식한 1인용 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차분한 올리브빛 쿠션과 부드럽게 휘어진 등받이가 여유로운 분위기를 더해주는 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_PC_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싱그러운 초록빛 프레임과 푹신한 청록빛 쿠션이 어우러진 아늑한 1인용 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러운 버터빛 쿠션과 빨간 다리가 귀여운 포인트를 더해주는 심플한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Synthesizer_Stand_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산뜻한 파란 프레임과 푹신한 쿠션으로 편안한 자세를 잡아주는 독특한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싱그러운 초록빛 쿠션과 따뜻한 원목 프레임이 어우러진 포근한 1인용 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Fireplace_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돌돌 말린 듯한 푹신한 쿠션과 둥근 원목 프레임이 어우러진 개성 있는 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따뜻한 꿀빛 색감과 둥글게 이어진 프레임이 돋보이는 아늑한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방 한쪽 모서리에 쏙 들어가 따뜻한 분위기를 만들어주는 벽난로.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_PC_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따뜻한 원목 프레임과 폭신한 쿠션이 어우러진 편안한 안락의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선명한 블루 쿠션과 레드 프레임이 어우러진 스포티한 게이밍 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Pouf_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도넛처럼 동그랗고 폭신해서 포근하게 몸을 맡길 수 있는 푸프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_PC_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>높게 솟은 굴뚝과 따뜻한 색감이 아늑한 분위기를 더해주는 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화사한 베리빛 쿠션과 푹신한 팔걸이가 포인트인 사무용 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포근한 구름빛 쿠션과 따뜻한 원목 프레임이 어우러진 아늑한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싱그러운 초록빛과 통통한 실루엣이 귀여움을 더해주는 아담한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑크 젤리 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_TV_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Toy_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허니 라운드 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리 원목 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_TV_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>올리브 라운지 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑크 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Toy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스카이 밸런스 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>민트 레트로 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아쿠아 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Toy_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>롤링 쿠션 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_TV_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앤티크 그린 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아쿠아 오피스 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벽돌 굴뚝 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Darts_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Audio_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Ball_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Audio_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Mouse_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Audio_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Audio_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Piano_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Guitar_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블랙 이그제큐티브 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Barbell_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Audio_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Audio_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Audio_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>컬러풀 카세트 플레이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Audio_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Keyboard_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Barbell_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_PC_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러운 핑크빛 물결무늬가 사랑스러운 분위기를 더해주는 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Treadmill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨갛게 타오르는 장작불로 햄찌의 공간을 따뜻하게 데워주는 난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Pouf_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Dumbbell_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Computer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Pouf_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Pouf_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>헤드폰을 쓰고 나만의 음악에 푹 빠질 수 있는 카세트 플레이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Dumbbell_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여러 가지 모양을 만들며 가지고 놀 수 있는 알록달록한 블록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고운 선율로 햄찌의 공간을 우아하게 채워주는 클래식 피아노</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빙글빙글 돌아가는 레코드와 함께 감성에 빠져볼 수 있는 턴테이블</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Guitar_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Bed_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_PC_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Pouf_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Pouf_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Pouf_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Fireplace_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Armchair_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Chair_PC_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>햄찌의 숨겨둔 노래 실력을 마음껏 뽐낼 수 있는 알록달록 마이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라운드 화로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화로 난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plants</x:t>
+  </x:si>
   <x:si>
     <x:t>벽돌 벽난로</x:t>
   </x:si>
   <x:si>
+    <x:t>굴뚝 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미니 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>꽃잎 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청록 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통통 푸프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이지 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라벤더 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새싹 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Music</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>튼튼한 바벨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>올리브 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블록 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 변기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리 빈백</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새싹 푸프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀크티 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다육이 화분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초원 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿠키 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레드 바 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둥근 변기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몽글 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>링 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>추억의 라디오</x:t>
+  </x:si>
+  <x:si>
+    <x:t>항구 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대리석 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도넛 푸프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>와이드 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑크 덤벨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둥실 흔들의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벽난로 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>민트링 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>황혼 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보라색 마우스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미니 컴퓨터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>댄싱 붐박스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>팝팝 스피커</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리듬 북</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실내 자전거</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식 덤벨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해변 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알록달록 공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상위 카테고리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고리 쌓기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사막빛 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보라색 키보드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테라 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하위 카테고리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월넛 흔들의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캔디팝 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박빛 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모래시계 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식 피아노</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레트로 변기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포옹 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>컬러 블록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장난감 자동차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>숲빛 흔들의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벽걸이 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바벨 벤치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장작 난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선인장 화분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carpet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모던 스테레오</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임 컨트롤러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레트로 게임기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>골드 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모던 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코너 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베리 바 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toilet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라운드 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원통 난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>런닝머신</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반달 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chair</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모던 변기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스탠드 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>느긋한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따뜻한 코코아빛과 도톰한 쿠션이 포근한 느낌을 더해주는 아늑한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Toilet_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둥글고 두툼한 등받이가 몸을 포근하게 감싸주는 아늑한 1인용 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Synthesizer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따뜻한 원목 프레임과 짙은 브라운 쿠션이 어우러진 여유로운 흔들의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Toilet_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따스한 햇살을 닮은 노란 쿠션과 주황빛 프레임이 돋보이는 편안한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Synthesizer_Stand_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시원한 아쿠아빛 쿠션과 심플한 디자인이 돋보이는 깔끔한 사무용 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_PC_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싱그러운 초록빛 쿠션과 따뜻한 원목 프레임이 어우러진 편안한 흔들의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은은한 세이지 그린 좌판과 짙은 프레임이 어우러진 심플한 높은 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_PC_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 베리빛 쿠션과 도톰한 팔걸이가 아늑함을 더해주는 1인용 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말랑한 젤리를 닮은 둥근 실루엣과 화사한 핑크빛이 돋보이는 아담한 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Toilet_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_PC_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_BarbellStand_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따뜻한 오렌지빛 프레임과 폭신한 쿠션으로 편안함을 더한 게이밍 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_ExerciseBike_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러운 살구빛과 도톰한 쿠션이 아늑한 분위기를 더해주는 포근한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>깔끔하고 심플한 디자인으로 공간에 따뜻한 분위기를 더해주는 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_GameConsole_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_GameConsole_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_GameConsole_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Plants_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Chair_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선명한 체리빛 쿠션과 부드러운 원목 프레임이 어우러진 포근한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>묵직한 블랙 쿠션과 넓은 등받이로 고급스러운 분위기를 더한 사무용 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다양한 소리와 리듬으로 햄찌만의 음악을 만들어볼 수 있는 신디사이저</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차분한 회색빛 쿠션과 따뜻한 원목 다리가 어우러진 깔끔하고 편안한 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따뜻한 브릭 컬러의 둥근 좌판과 차분한 프레임이 어우러진 심플한 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Plants_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Armchair_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Decoration_Carpet_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Furniture_Toilet_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Minihome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새싹 포근 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스탠드 신디사이저</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라일락 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새싹 포근 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>햇살 라운지 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>살구 포근 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>햇살 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새싹 꼬마 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식 브라운 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>느긋한 원목 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파도 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubCategory</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디지털 신디사이저</x:t>
+  </x:si>
+  <x:si>
+    <x:t>햇살 2층 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이싱 블루 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베리 쿠션 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포레스트 쿠션 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심플 2층 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가을 들판 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복숭아 링 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포근 그레이 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분홍 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버터 쿠션 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑크 더블 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새싹 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코랄 더블 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구름 원목 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알록달록 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>올리브 더블 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말랑 큐브 푸프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>햇살 접이식 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구름같이 푹신한 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노을 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호두나무 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 쿠션 소파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포레스트 쿠션 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레트로 카세트 라디오</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알록달록 마이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fireplace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초록숲 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허니 게이밍 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑크 웨이브 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아쿠아 더블 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_TV_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퍼플 프레임 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벚꽃 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>올리브 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코랄 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Toy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포근 벤치 푸프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Electronics</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Exercise</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지 미니 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>추억의 턴테이블</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_TV_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Toy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하늘 싱글 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베리 오피스 체어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Toy_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레트로 조이스틱</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_TV_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코코아 포근 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옐로우 레트로 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_TV_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Minihome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Carousel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Darts_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Dumbbell_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭신한 쿠션에 쏙 기대어 편안하게 쉬기 좋은 푸프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Keyboard_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둥글둥글한 디자인이 편안한 느낌을 주는 변기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둥근 형태와 따뜻한 색감이 어우러진 작은 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Mouse_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노란색 테두리가 돋보이는 레트로 감성의 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따스한 햇살빛 프레임이 돋보이는 아늑한 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Computer_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>햄찌들이 둘이서도 포근하게 쉴 수 있는 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알록달록한 색감이 기분까지 밝게 해주는 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사각 좌판과 교차된 프레임이 돋보이는 튼튼한 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Dumbbell_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싱그러운 초록빛이 편안한 숲을 떠올리게 하는 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원목이 단단해 흔들림이 전혀 없는 2층 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산뜻한 민트색이 돋보이는 레트로 디자인의 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Plants_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실내에서 편하게 달리기를 즐길 수 있는 런닝머신</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Audio_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따뜻하고 포근한 분위기를 더해주는 붉은빛 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Audio_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Audio_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Guitar_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>푸른 하늘과 싱그러운 초원을 닮은 산뜻한 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은은한 라일락빛과 포근한 분홍빛이 어우러진 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Audio_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Audio_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Audio_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Audio_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 복숭아를 닮은 부드러운 색감의 원형 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바벨 운동을 편하게 즐길 수 있는 벤치 세트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Barbell_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싱그러운 초록빛에 폭신한 쿠션을 더한 아늑한 푸프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통통 두드리며 신나는 리듬을 즐길 수 있는 북</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알록달록한 고리를 차곡차곡 쌓아 올리는 장난감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따뜻한 색감과 작은 다리가 어우러진 클래식한 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길쭉한 다리가 달린 독특한 디자인의 스탠드 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Carpet_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Audio_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Piano_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Decor/Plants_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Synthesizer_Stand_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말랑하고 폭신한 쿠션에 푹 기대어 쉬기 좋은 푸프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>알록달록한 버튼으로 게임을 즐길 수 있는 컨트롤러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러운 밀크티를 닮은 따뜻한 색감의 원형 카펫</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Furniture/Bed_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잘록한 모래시계 모양이 돋보이는 독특한 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고풍스러운 장식과 굴뚝이 어우러진 클래식 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짙은 청록빛으로 차분한 분위기를 더해주는 벽난로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둥근 화로 속 불씨가 은은한 온기를 전해주는 난로</x:t>
+  </x:si>
+  <x:si>
     <x:t>붉은 벽돌의 따뜻한 분위기가 느껴지는 벽난로</x:t>
   </x:si>
   <x:si>
@@ -33,2309 +2067,347 @@
     <x:t>높게 솟은 붉은 굴뚝이 돋보이는 벽돌 벽난로</x:t>
   </x:si>
   <x:si>
-    <x:t>블록처럼 단순하고 통통한 모양이 매력적인 작은 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>둥근 좌판과 부드럽게 휘어진 다리가 어우러진 산뜻한 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_TV_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화사한 벚꽃빛 침구가 포근한 분위기를 더해주는 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흔들면 재미있는 소리가 날 것 같은 알록달록한 딸랑이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>편하게 기대어 느긋한 시간을 보내기 좋은 나무 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폭신한 둥근 좌판과 따뜻한 우드톤이 어우러진 아담한 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>꽃잎처럼 포근하게 감싸주는 사랑스러운 분홍빛 1인용 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>톡톡 튀는 베리 컬러와 둥근 프레임이 매력적인 높은 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은은한 보랏빛이 공간을 포근하게 채워주는 1인용 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_TV_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>둥근 장식 프레임과 짙은 초록빛이 어우러진 클래식한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_TV_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Pouf_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Pouf_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Toy_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Pouf_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동글동글한 좌판과 통통한 다리가 귀여운 포인트 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_TV_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>싱그러운 색감과 둥근 등받이가 어우러진 포근한 안락의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>푹신한 쿠션과 깔끔한 디자인이 돋보이는 파란색 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Treadmill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Pouf_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따스한 모래빛과 시원한 바다빛이 어우러진 포근한 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따스한 가을 들판을 닮은 색감이 아늑함을 더해주는 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Audio_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따뜻한 선율로 햄찌의 하루를 감성 가득 채워주는 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/BarbellStand_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Audio_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Audio_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스탠드에 올려 더욱 편하게 연주할 수 있는 신디사이저</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Toy_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Pouf_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따스한 호박빛 색감이 아늑한 분위기를 더해주는 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_TV_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공주들은 작은 침대는 사치라는 것을 깨닫게 해주는 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/GameConsole_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Toy_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신나는 음악에 맞춰 절로 몸이 들썩이는 알록달록 붐박스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Audio_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Ball_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/ExerciseBike_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Audio_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풍성한 사운드로 햄찌의 공간을 가득 채워주는 스테레오</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잔잔한 음악과 함께 느긋한 시간을 보낼 수 있는 라디오</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Audio_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빙글빙글 돌리며 가지고 놀 수 있는 알록달록한 팽이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Audio_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_TV_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/GameConsole_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Darts_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Mouse_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/GameConsole_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Toy_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Toy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Toilet_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따스한 황혼빛 색감과 기하학 무늬가 어우러진 포근한 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Pouf_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_TV_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>짙은 원목 프레임이 편안하고 아늑한 느낌을 주는 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산뜻한 민트빛 원형 무늬가 포인트가 되는 포근한 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신나는 음악으로 햄찌의 하루를 즐겁게 채워주는 스피커</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Piano_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>싱그러운 색감으로 공간에 생기를 더해주는 산뜻한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Toilet_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Pouf_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Toilet_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Toilet_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따스한 모랫빛과 짙은 푸른빛이 어우러진 멋스러운 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>톡톡 튀는 색감과 레트로한 감성이 매력적인 카세트 라디오</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동글동글 폭신한 쿠션에 앉아 편안하게 쉬기 좋은 푸프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우아한 기둥 장식이 돋보이는 고급스러운 분위기의 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선명한 레드 쿠션과 메탈 프레임이 어우러진 깔끔한 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동글동글한 좌판과 세 개의 다리가 어우러진 아담한 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Synthesizer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Toy_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Audio_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반달 모양의 등받이가 포인트인 아담하고 귀여운 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초록빛 쿠션과 주황색 프레임이 어우러진 포근한 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미니 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청록 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화로 난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라운드 화로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>팽이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다트판</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸랑이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Pouf_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Dumbbell_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Dumbbell_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Toilet_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본적인 디자인의 묵직한 덤벨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Pouf_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전국 모든 딸들이 탐내는 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Keyboard_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Computer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혼자 쉬기 딱 좋은 아늑한 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Synthesizer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_GameConsole_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밝은 핑크색이 돋보이는 가벼운 덤벨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Pouf_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_GameConsole_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_GameConsole_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Toilet_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Pouf_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Pouf_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Pouf_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Toilet_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Treadmill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자연의 색감을 담은 편안한 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Toilet_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작지만 존재감 있는 초록 친구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>넓고 튼튼한 프레임의 포근한 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Pouf_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Bed_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따뜻한 분위기가 느껴지는 원목 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Audio_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Darts_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Audio_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Audio_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Ball_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Mouse_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Audio_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Barbell_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블랙 이그제큐티브 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Piano_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Audio_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Audio_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Audio_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Guitar_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Audio_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>컬러풀 카세트 플레이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>싱그러운 초록빛 쿠션과 따뜻한 원목 프레임이 어우러진 포근한 1인용 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드러운 버터빛 쿠션과 빨간 다리가 귀여운 포인트를 더해주는 심플한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돌돌 말린 듯한 푹신한 쿠션과 둥근 원목 프레임이 어우러진 개성 있는 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Synthesizer_Stand_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>싱그러운 초록빛 프레임과 푹신한 청록빛 쿠션이 어우러진 아늑한 1인용 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산뜻한 파란 프레임과 푹신한 쿠션으로 편안한 자세를 잡아주는 독특한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Fireplace_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>깊은 브라운빛 쿠션과 겹겹이 나뉜 등받이가 편안함을 더해주는 클래식한 1인용 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상큼한 청록빛 프레임과 달콤한 핑크빛 쿠션이 톡톡 튀는 분위기를 더해주는 1인용 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>차분한 올리브빛 쿠션과 부드럽게 휘어진 등받이가 여유로운 분위기를 더해주는 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>굴뚝 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plants</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통통 푸프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>꽃잎 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>올리브 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대리석 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리 빈백</x:t>
-  </x:si>
-  <x:si>
-    <x:t>튼튼한 바벨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초원 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Music</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몽글 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도넛 푸프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새싹 푸프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>링 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레드 바 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 변기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿠키 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이지 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>둥근 변기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새싹 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다육이 화분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>추억의 라디오</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라벤더 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>항구 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블록 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀크티 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상위 카테고리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미니 컴퓨터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벽난로 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>댄싱 붐박스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해변 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고리 쌓기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보라색 마우스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식 덤벨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>팝팝 스피커</x:t>
-  </x:si>
-  <x:si>
-    <x:t>와이드 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리듬 북</x:t>
-  </x:si>
-  <x:si>
-    <x:t>민트링 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>황혼 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실내 자전거</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알록달록 공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핑크 덤벨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>둥실 흔들의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박빛 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레트로 게임기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식 피아노</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캔디팝 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>컬러 블록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월넛 흔들의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carpet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사막빛 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선인장 화분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벽걸이 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보라색 키보드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>모던 스테레오</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장난감 자동차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>모래시계 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>게임 컨트롤러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>숲빛 흔들의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테라 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바벨 벤치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포옹 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장작 난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하위 카테고리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레트로 변기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코너 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라운드 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>느긋한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>런닝머신</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toilet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Chair</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베리 바 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>모던 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스탠드 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반달 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>모던 변기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방 한쪽 모서리에 쏙 들어가 따뜻한 분위기를 만들어주는 벽난로.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_PC_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따뜻한 꿀빛 색감과 둥글게 이어진 프레임이 돋보이는 아늑한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따뜻한 원목 프레임과 폭신한 쿠션이 어우러진 편안한 안락의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선명한 블루 쿠션과 레드 프레임이 어우러진 스포티한 게이밍 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>싱그러운 초록빛과 통통한 실루엣이 귀여움을 더해주는 아담한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Pouf_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도넛처럼 동그랗고 폭신해서 포근하게 몸을 맡길 수 있는 푸프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_PC_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>높게 솟은 굴뚝과 따뜻한 색감이 아늑한 분위기를 더해주는 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화사한 베리빛 쿠션과 푹신한 팔걸이가 포인트인 사무용 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포근한 구름빛 쿠션과 따뜻한 원목 프레임이 어우러진 아늑한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Guitar_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Dumbbell_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_PC_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_PC_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>깔끔하고 심플한 디자인으로 공간에 따뜻한 분위기를 더해주는 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Plants_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_GameConsole_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Plants_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선명한 체리빛 쿠션과 부드러운 원목 프레임이 어우러진 포근한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>묵직한 블랙 쿠션과 넓은 등받이로 고급스러운 분위기를 더한 사무용 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_GameConsole_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다양한 소리와 리듬으로 햄찌만의 음악을 만들어볼 수 있는 신디사이저</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Toilet_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>차분한 회색빛 쿠션과 따뜻한 원목 다리가 어우러진 깔끔하고 편안한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따뜻한 브릭 컬러의 둥근 좌판과 차분한 프레임이 어우러진 심플한 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드러운 살구빛과 도톰한 쿠션이 아늑한 분위기를 더해주는 포근한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_GameConsole_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따스한 햇살을 닮은 노란 쿠션과 주황빛 프레임이 돋보이는 편안한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Toilet_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Synthesizer_Stand_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 베리빛 쿠션과 도톰한 팔걸이가 아늑함을 더해주는 1인용 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Toilet_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>둥글고 두툼한 등받이가 몸을 포근하게 감싸주는 아늑한 1인용 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따뜻한 코코아빛과 도톰한 쿠션이 포근한 느낌을 더해주는 아늑한 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Synthesizer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Toilet_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말랑한 젤리를 닮은 둥근 실루엣과 화사한 핑크빛이 돋보이는 아담한 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시원한 아쿠아빛 쿠션과 심플한 디자인이 돋보이는 깔끔한 사무용 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따뜻한 원목 프레임과 짙은 브라운 쿠션이 어우러진 여유로운 흔들의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>싱그러운 초록빛 쿠션과 따뜻한 원목 프레임이 어우러진 편안한 흔들의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_BarbellStand_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_PC_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_PC_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은은한 세이지 그린 좌판과 짙은 프레임이 어우러진 심플한 높은 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_PC_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따뜻한 오렌지빛 프레임과 폭신한 쿠션으로 편안함을 더한 게이밍 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Armchair_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Decoration_Carpet_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_ExerciseBike_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Chair_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여러 가지 모양을 만들며 가지고 놀 수 있는 알록달록한 블록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>헤드폰을 쓰고 나만의 음악에 푹 빠질 수 있는 카세트 플레이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고운 선율로 햄찌의 공간을 우아하게 채워주는 클래식 피아노</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빙글빙글 돌아가는 레코드와 함께 감성에 빠져볼 수 있는 턴테이블</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_PC_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Pouf_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Pouf_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Pouf_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Pouf_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Treadmill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빨갛게 타오르는 장작불로 햄찌의 공간을 따뜻하게 데워주는 난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Pouf_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Bed_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_PC_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드러운 핑크빛 물결무늬가 사랑스러운 분위기를 더해주는 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Keyboard_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Dumbbell_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Computer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Furniture_Pouf_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Fireplace_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Furniture/Play_Barbell_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Armchair_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Chair_PC_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>햄찌의 숨겨둔 노래 실력을 마음껏 뽐낼 수 있는 알록달록 마이크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라일락 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새싹 포근 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스탠드 신디사이저</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파도 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심플 2층 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>햇살 2층 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>햇살 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>햇살 라운지 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>느긋한 원목 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SubCategory</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새싹 포근 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베리 쿠션 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>살구 포근 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식 브라운 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새싹 꼬마 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디지털 신디사이저</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레이싱 블루 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포레스트 쿠션 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버터 쿠션 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코랄 더블 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분홍 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구름 원목 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포근 그레이 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핑크 더블 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알록달록 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말랑 큐브 푸프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가을 들판 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>햇살 접이식 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>올리브 더블 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구름같이 푹신한 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복숭아 링 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새싹 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레트로 카세트 라디오</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 쿠션 소파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핑크 웨이브 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fireplace</x:t>
-  </x:si>
-  <x:si>
-    <x:t>올리브 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퍼플 프레임 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노을 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포레스트 쿠션 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호두나무 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벚꽃 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허니 게이밍 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알록달록 마이크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초록숲 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아쿠아 더블 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_TV_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코랄 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Exercise</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하늘 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_TV_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포근 벤치 푸프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지 미니 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>추억의 턴테이블</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코코아 포근 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Toy_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_TV_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레트로 조이스틱</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Electronics</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옐로우 레트로 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Toy_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Toy_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_TV_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베리 오피스 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허니 라운드 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_TV_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_TV_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핑크 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>올리브 라운지 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Toy_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스카이 밸런스 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리 원목 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>롤링 쿠션 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_TV_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Toy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>민트 레트로 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아쿠아 싱글 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핑크 젤리 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Toy_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아쿠아 오피스 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앤티크 그린 체어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폭신한 쿠션에 쏙 기대어 편안하게 쉬기 좋은 푸프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Darts_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Dumbbell_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사각 좌판과 교차된 프레임이 돋보이는 튼튼한 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Keyboard_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Mouse_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>둥근 형태와 따뜻한 색감이 어우러진 작은 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Dumbbell_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>둥글둥글한 디자인이 편안한 느낌을 주는 변기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노란색 테두리가 돋보이는 레트로 감성의 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>햄찌들이 둘이서도 포근하게 쉴 수 있는 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따스한 햇살빛 프레임이 돋보이는 아늑한 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알록달록한 색감이 기분까지 밝게 해주는 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Computer_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Plants_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>싱그러운 초록빛이 편안한 숲을 떠올리게 하는 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산뜻한 민트색이 돋보이는 레트로 디자인의 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원목이 단단해 흔들림이 전혀 없는 2층 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Audio_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따뜻하고 포근한 분위기를 더해주는 붉은빛 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은은한 라일락빛과 포근한 분홍빛이 어우러진 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Audio_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 복숭아를 닮은 부드러운 색감의 원형 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Audio_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Audio_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Guitar_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>푸른 하늘과 싱그러운 초원을 닮은 산뜻한 카펫</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Audio_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Audio_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Audio_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실내에서 편하게 달리기를 즐길 수 있는 런닝머신</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Piano_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길쭉한 다리가 달린 독특한 디자인의 스탠드 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따뜻한 색감과 작은 다리가 어우러진 클래식한 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Carpet_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Audio_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바벨 운동을 편하게 즐길 수 있는 벤치 세트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알록달록한 고리를 차곡차곡 쌓아 올리는 장난감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>싱그러운 초록빛에 폭신한 쿠션을 더한 아늑한 푸프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통통 두드리며 신나는 리듬을 즐길 수 있는 북</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Barbell_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잘록한 모래시계 모양이 돋보이는 독특한 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_Synthesizer_Stand_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말랑하고 폭신한 쿠션에 푹 기대어 쉬기 좋은 푸프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Furniture/Bed_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Decor/Plants_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>알록달록한 버튼으로 게임을 즐길 수 있는 컨트롤러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드러운 밀크티를 닮은 따뜻한 색감의 원형 카펫</x:t>
+    <x:t>싱그러운 색감이 돋보이는 산뜻한 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_PC_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시원한 파도빛을 담은 깔끔하고 산뜻한 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따스한 햇살과 푸른 하늘을 담은 듯한 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>따스한 노을빛을 닮은 포근한 색감의 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둥근 발받침이 더해진 심플하고 편안한 스툴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마치 공주가 된 것 같은 느낌을 주는 침대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시원한 색감으로 편안한 잠을 선물하는 침대</x:t>
   </x:si>
   <x:si>
     <x:t>Furniture_Armchair_07</x:t>
   </x:si>
   <x:si>
+    <x:t>Furniture_Armchair_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_13</x:t>
+  </x:si>
+  <x:si>
     <x:t>Furniture_Armchair_20</x:t>
   </x:si>
   <x:si>
     <x:t>둥글둥글한 모양이 귀여운 포근한 흔들의자</x:t>
   </x:si>
   <x:si>
-    <x:t>싱그러운 색감이 돋보이는 산뜻한 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마치 공주가 된 것 같은 느낌을 주는 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_PC_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시원한 파도빛을 담은 깔끔하고 산뜻한 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따스한 노을빛을 닮은 포근한 색감의 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>따스한 햇살과 푸른 하늘을 담은 듯한 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>둥근 발받침이 더해진 심플하고 편안한 스툴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시원한 색감으로 편안한 잠을 선물하는 침대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_12</x:t>
+    <x:t>Furniture_Fireplace_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Fireplace_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Fireplace_04</x:t>
   </x:si>
   <x:si>
     <x:t>Furniture_Armchair_04</x:t>
   </x:si>
   <x:si>
+    <x:t>Furniture_Chair_PC_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decoration_Carpet_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Fireplace_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Fireplace_10</x:t>
+  </x:si>
+  <x:si>
     <x:t>Decoration_Carpet_07</x:t>
   </x:si>
   <x:si>
+    <x:t>Furniture_Fireplace_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노란빛이 산뜻한 실용적인 접이식 의자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/TV_03</x:t>
+  </x:si>
+  <x:si>
     <x:t>Furniture_Chair_PC_04</x:t>
   </x:si>
   <x:si>
+    <x:t>줄을 당겨 물을 내리는 독특한 레트로 변기</x:t>
+  </x:si>
+  <x:si>
     <x:t>군더더기 없이 깔끔한 기본 디자인의 변기</x:t>
   </x:si>
   <x:si>
+    <x:t>Decoration_Carpet_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Fireplace_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Armchair_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/TV_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decoration_Carpet_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Toy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decoration_Carpet_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Fireplace_09</x:t>
+  </x:si>
+  <x:si>
     <x:t>Furniture_Fireplace_06</x:t>
   </x:si>
   <x:si>
-    <x:t>줄을 당겨 물을 내리는 독특한 레트로 변기</x:t>
+    <x:t>Furniture_Armchair_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Fireplace_07</x:t>
   </x:si>
   <x:si>
     <x:t>짙은 갈색과 푸른빛이 어우러진 포근한 카펫</x:t>
   </x:si>
   <x:si>
-    <x:t>Furniture_Chair_PC_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_09</x:t>
+    <x:t>Furniture_Fireplace_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Fireplace_03</x:t>
   </x:si>
   <x:si>
     <x:t>Furniture_Chair_PC_02</x:t>
   </x:si>
   <x:si>
-    <x:t>Furniture_Armchair_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Armchair_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노란빛이 산뜻한 실용적인 접이식 의자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/TV_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/TV_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Toy_02</x:t>
+    <x:t>Image/Item/Play/Toy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/TV_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decoration_Carpet_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decoration_Carpet_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파란색과 노란색이 어우러진 알록달록한 공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decoration_Plants_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반듯하고 깔끔한 디자인의 모던한 변기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러운 보라색이 돋보이는 심플한 키보드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decoration_Carpet_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/TV_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Fireplace_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Chair_PC_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실내에서 간편하게 운동할 수 있는 자전거</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decoration_Carpet_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decoration_Carpet_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Toy_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옛날 감성이 느껴지는 아담한 크기의 게임기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decoration_Carpet_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Toy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>둥글고 귀여운 디자인의 보라색 마우스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가볍게 다트 놀이를 즐길 수 있는 다트판</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작은 화면이 달린 심플한 디자인의 컴퓨터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_ExerciseBike_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>푹 파묻혀 느긋하게 쉬기 좋은 포근한 빈백</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군더더기 없이 깔끔한 디자인의 벽걸이 TV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작고 귀여운 디자인의 빨간 장난감 자동차</x:t>
   </x:si>
   <x:si>
     <x:t>Play_BarbellStand_01</x:t>
   </x:si>
   <x:si>
+    <x:t>Decoration_Carpet_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조이스틱과 버튼이 달린 클래식한 게임기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Furniture_Fireplace_11</x:t>
+  </x:si>
+  <x:si>
     <x:t>Image/Item/Play/Ball_01</x:t>
   </x:si>
   <x:si>
-    <x:t>반듯하고 깔끔한 디자인의 모던한 변기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Toy_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>푹 파묻혀 느긋하게 쉬기 좋은 포근한 빈백</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실내에서 간편하게 운동할 수 있는 자전거</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군더더기 없이 깔끔한 디자인의 벽걸이 TV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>둥글고 귀여운 디자인의 보라색 마우스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/Toy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드러운 보라색이 돋보이는 심플한 키보드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옛날 감성이 느껴지는 아담한 크기의 게임기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_09</x:t>
-  </x:si>
-  <x:si>
     <x:t>Image/Item/Play/Toy_06</x:t>
   </x:si>
   <x:si>
-    <x:t>Image/Item/Play/Toy_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조이스틱과 버튼이 달린 클래식한 게임기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/TV_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가볍게 다트 놀이를 즐길 수 있는 다트판</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작은 화면이 달린 심플한 디자인의 컴퓨터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작고 귀여운 디자인의 빨간 장난감 자동차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/TV_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Play_ExerciseBike_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Plants_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Chair_PC_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Furniture_Fireplace_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decoration_Carpet_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파란색과 노란색이 어우러진 알록달록한 공</x:t>
+    <x:t>Image/Item/Play/TV_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/TV_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싱그러운 분위기를 더해 주는 작은 화분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근력 운동에 사용하기 좋은 기본 바벨</x:t>
   </x:si>
   <x:si>
     <x:t>Image/Item/Play/Toy_04</x:t>
   </x:si>
   <x:si>
+    <x:t>작은 공간에도 쏙 들어가는 아담한 벽난로</x:t>
+  </x:si>
+  <x:si>
     <x:t>Decoration_Plants_02</x:t>
   </x:si>
   <x:si>
+    <x:t>Image/Item/Play/TV_06</x:t>
+  </x:si>
+  <x:si>
     <x:t>넓은 화면과 심플한 디자인이 돋보이는 TV</x:t>
   </x:si>
   <x:si>
-    <x:t>싱그러운 분위기를 더해 주는 작은 화분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/TV_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>근력 운동에 사용하기 좋은 기본 바벨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/TV_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Item/Play/TV_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>골드 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벽돌 굴뚝 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작은 공간에도 쏙 들어가는 아담한 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>둥근 화로 속 불씨가 은은한 온기를 전해주는 난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빨갛게 달아오른 불씨가 포근한 온기를 전해주는 화로 난로</x:t>
-  </x:si>
-  <x:si>
     <x:t>은은한 금빛 장식으로 포인트를 더한 벽난로</x:t>
   </x:si>
   <x:si>
-    <x:t>짙은 청록빛으로 차분한 분위기를 더해주는 벽난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원통 난로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고풍스러운 장식과 굴뚝이 어우러진 클래식 벽난로</x:t>
+    <x:t>Prefabs/Furniture/Play_Carousel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Item/Play/Slide</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매달려 놀기 딱 좋은 햄스터 타워</x:t>
+  </x:si>
+  <x:si>
+    <x:t>햄스터 타워</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Wheel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Play_Slide</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Tower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Furniture/Play_Slide</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간 작은 방</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -2405,6 +2477,26 @@
           <x:name val="&quot;맑은 고딕&quot;"/>
           <x:sz val="10"/>
           <x:color rgb="ff008000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="돋움"/>
+          <x:sz val="12"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="돋움"/>
+          <x:sz val="12"/>
+          <x:color rgb="ff000000"/>
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -2497,7 +2589,7 @@
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -2563,6 +2655,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -3169,7 +3264,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:M153"/>
+  <x:dimension ref="A1:M158"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="16" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.5546875" style="2" customWidth="1"/>
@@ -3187,50 +3282,50 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" s="3" customFormat="1" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H1" s="1"/>
       <x:c r="I1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:10" s="5" customFormat="1" customHeight="1">
       <x:c r="A2" s="4" t="s">
-        <x:v>286</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B2" s="4" t="s">
-        <x:v>286</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="C2" s="4" t="s">
-        <x:v>286</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D2" s="4" t="s">
-        <x:v>286</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="E2" s="4" t="s">
-        <x:v>286</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="F2" s="4" t="s">
-        <x:v>286</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="G2" s="4" t="s">
-        <x:v>286</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="H2" s="4"/>
       <x:c r="I2" s="4"/>
@@ -3238,25 +3333,25 @@
     </x:row>
     <x:row r="3" spans="1:13" s="7" customFormat="1" customHeight="1">
       <x:c r="A3" s="6" t="s">
-        <x:v>109</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>292</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>570</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>525</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>504</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>518</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="G3" s="8" t="s">
-        <x:v>513</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="H3" s="21"/>
       <x:c r="I3" s="21"/>
@@ -3267,25 +3362,25 @@
     </x:row>
     <x:row r="4" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A4" s="12" t="s">
-        <x:v>135</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B4" s="12" t="s">
-        <x:v>526</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="C4" s="12" t="s">
-        <x:v>598</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="D4" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E4" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="12" t="s">
-        <x:v>584</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="G4" s="15" t="s">
-        <x:v>330</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="H4" s="9"/>
       <x:c r="I4" s="9"/>
@@ -3296,25 +3391,25 @@
     </x:row>
     <x:row r="5" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A5" s="12" t="s">
-        <x:v>171</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B5" s="12" t="s">
-        <x:v>543</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s">
-        <x:v>686</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="D5" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E5" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F5" s="12" t="s">
-        <x:v>656</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="G5" s="15" t="s">
-        <x:v>450</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="H5" s="9"/>
       <x:c r="I5" s="9"/>
@@ -3325,25 +3420,25 @@
     </x:row>
     <x:row r="6" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A6" s="12" t="s">
-        <x:v>181</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B6" s="12" t="s">
-        <x:v>575</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C6" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E6" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F6" s="12" t="s">
-        <x:v>648</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="G6" s="15" t="s">
-        <x:v>314</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="H6" s="9"/>
       <x:c r="I6" s="9"/>
@@ -3354,25 +3449,25 @@
     </x:row>
     <x:row r="7" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A7" s="12" t="s">
-        <x:v>176</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B7" s="12" t="s">
-        <x:v>534</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="C7" s="12" t="s">
-        <x:v>164</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D7" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E7" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="12" t="s">
-        <x:v>587</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="G7" s="15" t="s">
-        <x:v>342</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="H7" s="9"/>
       <x:c r="I7" s="9"/>
@@ -3383,25 +3478,25 @@
     </x:row>
     <x:row r="8" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>175</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B8" s="12" t="s">
-        <x:v>545</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="C8" s="12" t="s">
-        <x:v>183</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D8" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E8" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="12" t="s">
-        <x:v>581</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="G8" s="15" t="s">
-        <x:v>323</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="H8" s="9"/>
       <x:c r="I8" s="9"/>
@@ -3412,25 +3507,25 @@
     </x:row>
     <x:row r="9" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A9" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>515</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="C9" s="12" t="s">
-        <x:v>177</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D9" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E9" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F9" s="12" t="s">
-        <x:v>650</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="G9" s="15" t="s">
-        <x:v>312</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="H9" s="9"/>
       <x:c r="I9" s="9"/>
@@ -3441,25 +3536,25 @@
     </x:row>
     <x:row r="10" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A10" s="12" t="s">
-        <x:v>128</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B10" s="12" t="s">
-        <x:v>565</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C10" s="12" t="s">
-        <x:v>664</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="D10" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>590</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="G10" s="15" t="s">
-        <x:v>318</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H10" s="9"/>
       <x:c r="I10" s="9"/>
@@ -3470,25 +3565,25 @@
     </x:row>
     <x:row r="11" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>170</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>520</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="C11" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D11" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E11" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F11" s="12" t="s">
-        <x:v>588</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="G11" s="15" t="s">
-        <x:v>327</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H11" s="9"/>
       <x:c r="I11" s="9"/>
@@ -3499,25 +3594,25 @@
     </x:row>
     <x:row r="12" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>179</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B12" s="12" t="s">
-        <x:v>547</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="C12" s="12" t="s">
-        <x:v>527</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D12" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E12" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F12" s="12" t="s">
-        <x:v>646</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="G12" s="15" t="s">
-        <x:v>328</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="H12" s="9"/>
       <x:c r="I12" s="9"/>
@@ -3528,25 +3623,25 @@
     </x:row>
     <x:row r="13" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>159</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>516</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="C13" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D13" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E13" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F13" s="12" t="s">
-        <x:v>583</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="G13" s="15" t="s">
-        <x:v>326</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="H13" s="9"/>
       <x:c r="I13" s="9"/>
@@ -3557,25 +3652,25 @@
     </x:row>
     <x:row r="14" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A14" s="12" t="s">
-        <x:v>166</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B14" s="12" t="s">
-        <x:v>499</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="C14" s="12" t="s">
-        <x:v>617</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="D14" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E14" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F14" s="12" t="s">
-        <x:v>605</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="G14" s="15" t="s">
-        <x:v>477</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="H14" s="9"/>
       <x:c r="I14" s="9"/>
@@ -3586,25 +3681,25 @@
     </x:row>
     <x:row r="15" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A15" s="12" t="s">
-        <x:v>182</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B15" s="12" t="s">
-        <x:v>529</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="C15" s="12" t="s">
-        <x:v>663</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="D15" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E15" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F15" s="12" t="s">
-        <x:v>591</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="G15" s="15" t="s">
-        <x:v>310</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H15" s="9"/>
       <x:c r="I15" s="9"/>
@@ -3615,25 +3710,25 @@
     </x:row>
     <x:row r="16" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A16" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>495</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="C16" s="12" t="s">
-        <x:v>625</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="D16" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E16" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F16" s="12" t="s">
-        <x:v>606</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="G16" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="H16" s="9"/>
       <x:c r="I16" s="9"/>
@@ -3644,25 +3739,25 @@
     </x:row>
     <x:row r="17" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A17" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
-        <x:v>501</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="C17" s="12" t="s">
-        <x:v>679</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="D17" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
-        <x:v>615</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="G17" s="15" t="s">
-        <x:v>324</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="H17" s="9"/>
       <x:c r="I17" s="9"/>
@@ -3673,25 +3768,25 @@
     </x:row>
     <x:row r="18" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A18" s="12" t="s">
-        <x:v>141</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>536</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="C18" s="12" t="s">
-        <x:v>673</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="D18" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F18" s="12" t="s">
-        <x:v>601</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="G18" s="15" t="s">
-        <x:v>337</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="H18" s="9"/>
       <x:c r="I18" s="9"/>
@@ -3702,25 +3797,25 @@
     </x:row>
     <x:row r="19" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A19" s="12" t="s">
-        <x:v>151</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B19" s="12" t="s">
-        <x:v>521</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="C19" s="12" t="s">
-        <x:v>600</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D19" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E19" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F19" s="12" t="s">
-        <x:v>642</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="G19" s="15" t="s">
-        <x:v>338</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="H19" s="9"/>
       <x:c r="I19" s="9"/>
@@ -3731,25 +3826,25 @@
     </x:row>
     <x:row r="20" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A20" s="12" t="s">
-        <x:v>123</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>538</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="C20" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F20" s="12" t="s">
-        <x:v>608</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="G20" s="15" t="s">
-        <x:v>320</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H20" s="9"/>
       <x:c r="I20" s="9"/>
@@ -3760,25 +3855,25 @@
     </x:row>
     <x:row r="21" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A21" s="12" t="s">
-        <x:v>168</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
-        <x:v>500</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="C21" s="12" t="s">
-        <x:v>599</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F21" s="12" t="s">
-        <x:v>604</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="G21" s="15" t="s">
-        <x:v>317</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="H21" s="9"/>
       <x:c r="I21" s="9"/>
@@ -3789,25 +3884,25 @@
     </x:row>
     <x:row r="22" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A22" s="12" t="s">
-        <x:v>158</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>498</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="C22" s="12" t="s">
-        <x:v>669</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F22" s="12" t="s">
-        <x:v>622</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="G22" s="15" t="s">
-        <x:v>316</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H22" s="9"/>
       <x:c r="I22" s="9"/>
@@ -3818,25 +3913,25 @@
     </x:row>
     <x:row r="23" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A23" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>542</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="C23" s="12" t="s">
-        <x:v>610</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="D23" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F23" s="12" t="s">
-        <x:v>603</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="G23" s="15" t="s">
-        <x:v>311</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H23" s="9"/>
       <x:c r="I23" s="9"/>
@@ -3847,25 +3942,25 @@
     </x:row>
     <x:row r="24" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A24" s="12" t="s">
-        <x:v>137</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>539</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="C24" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
-        <x:v>618</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="G24" s="15" t="s">
-        <x:v>336</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="H24" s="9"/>
       <x:c r="I24" s="9"/>
@@ -3876,25 +3971,25 @@
     </x:row>
     <x:row r="25" spans="1:13" s="14" customFormat="1" customHeight="1">
       <x:c r="A25" s="16" t="s">
-        <x:v>680</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="B25" s="16" t="s">
-        <x:v>248</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C25" s="16" t="s">
-        <x:v>16</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D25" s="16" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E25" s="16" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F25" s="16" t="s">
-        <x:v>492</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="G25" s="17" t="s">
-        <x:v>378</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H25" s="9"/>
       <x:c r="I25" s="9"/>
@@ -3905,25 +4000,25 @@
     </x:row>
     <x:row r="26" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A26" s="12" t="s">
-        <x:v>706</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>531</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="C26" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F26" s="12" t="s">
-        <x:v>331</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="G26" s="13" t="s">
-        <x:v>357</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H26" s="9"/>
       <x:c r="I26" s="9"/>
@@ -3934,25 +4029,25 @@
     </x:row>
     <x:row r="27" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A27" s="12" t="s">
-        <x:v>666</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
-        <x:v>505</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="C27" s="12" t="s">
-        <x:v>201</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D27" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E27" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F27" s="12" t="s">
-        <x:v>469</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="G27" s="13" t="s">
-        <x:v>366</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H27" s="9"/>
       <x:c r="I27" s="9"/>
@@ -3963,25 +4058,25 @@
     </x:row>
     <x:row r="28" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A28" s="12" t="s">
-        <x:v>689</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>226</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C28" s="12" t="s">
-        <x:v>13</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D28" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F28" s="12" t="s">
-        <x:v>325</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G28" s="13" t="s">
-        <x:v>362</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H28" s="9"/>
       <x:c r="I28" s="9"/>
@@ -3992,25 +4087,25 @@
     </x:row>
     <x:row r="29" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A29" s="12" t="s">
-        <x:v>672</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
-        <x:v>294</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C29" s="12" t="s">
-        <x:v>413</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="D29" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
-        <x:v>478</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G29" s="13" t="s">
-        <x:v>359</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H29" s="9"/>
       <x:c r="I29" s="9"/>
@@ -4021,25 +4116,25 @@
     </x:row>
     <x:row r="30" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A30" s="12" t="s">
-        <x:v>677</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>502</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="C30" s="12" t="s">
-        <x:v>408</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="D30" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E30" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F30" s="12" t="s">
-        <x:v>463</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="G30" s="13" t="s">
-        <x:v>107</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H30" s="9"/>
       <x:c r="I30" s="9"/>
@@ -4050,25 +4145,25 @@
     </x:row>
     <x:row r="31" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A31" s="12" t="s">
-        <x:v>660</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
-        <x:v>512</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C31" s="12" t="s">
-        <x:v>213</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F31" s="12" t="s">
-        <x:v>456</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="G31" s="13" t="s">
-        <x:v>380</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H31" s="9"/>
       <x:c r="I31" s="9"/>
@@ -4079,25 +4174,25 @@
     </x:row>
     <x:row r="32" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A32" s="12" t="s">
-        <x:v>678</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>503</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="C32" s="12" t="s">
-        <x:v>334</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D32" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F32" s="12" t="s">
-        <x:v>335</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="G32" s="13" t="s">
-        <x:v>361</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="H32" s="9"/>
       <x:c r="I32" s="9"/>
@@ -4108,25 +4203,25 @@
     </x:row>
     <x:row r="33" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A33" s="12" t="s">
-        <x:v>702</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="C33" s="12" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="E33" s="12" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="F33" s="12" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="G33" s="13" t="s">
         <x:v>496</x:v>
-      </x:c>
-      <x:c r="C33" s="12" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D33" s="12" t="s">
-        <x:v>578</x:v>
-      </x:c>
-      <x:c r="E33" s="12" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="F33" s="12" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="G33" s="13" t="s">
-        <x:v>441</x:v>
       </x:c>
       <x:c r="H33" s="9"/>
       <x:c r="I33" s="9"/>
@@ -4137,25 +4232,25 @@
     </x:row>
     <x:row r="34" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A34" s="12" t="s">
-        <x:v>668</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="B34" s="15" t="s">
-        <x:v>562</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C34" s="15" t="s">
-        <x:v>322</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D34" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
-        <x:v>479</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="G34" s="13" t="s">
-        <x:v>365</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H34" s="9"/>
       <x:c r="I34" s="9"/>
@@ -4166,25 +4261,25 @@
     </x:row>
     <x:row r="35" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A35" s="12" t="s">
-        <x:v>674</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="B35" s="15" t="s">
-        <x:v>566</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C35" s="15" t="s">
-        <x:v>222</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D35" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
-        <x:v>491</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="G35" s="13" t="s">
-        <x:v>383</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="H35" s="9"/>
       <x:c r="I35" s="9"/>
@@ -4195,25 +4290,25 @@
     </x:row>
     <x:row r="36" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A36" s="12" t="s">
-        <x:v>688</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="B36" s="15" t="s">
-        <x:v>517</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="C36" s="15" t="s">
-        <x:v>350</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
-        <x:v>482</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="G36" s="13" t="s">
-        <x:v>379</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H36" s="9"/>
       <x:c r="I36" s="9"/>
@@ -4224,25 +4319,25 @@
     </x:row>
     <x:row r="37" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A37" s="12" t="s">
-        <x:v>676</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="B37" s="15" t="s">
-        <x:v>571</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C37" s="15" t="s">
-        <x:v>210</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
-        <x:v>467</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="G37" s="13" t="s">
-        <x:v>375</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="H37" s="9"/>
       <x:c r="I37" s="9"/>
@@ -4253,25 +4348,25 @@
     </x:row>
     <x:row r="38" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A38" s="12" t="s">
-        <x:v>665</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="B38" s="15" t="s">
-        <x:v>506</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C38" s="15" t="s">
-        <x:v>411</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
-        <x:v>481</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="G38" s="13" t="s">
-        <x:v>384</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="H38" s="9"/>
       <x:c r="I38" s="9"/>
@@ -4282,25 +4377,25 @@
     </x:row>
     <x:row r="39" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A39" s="12" t="s">
-        <x:v>699</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="B39" s="15" t="s">
-        <x:v>552</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="C39" s="15" t="s">
-        <x:v>414</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F39" s="12" t="s">
-        <x:v>449</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="G39" s="13" t="s">
-        <x:v>358</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H39" s="9"/>
       <x:c r="I39" s="9"/>
@@ -4311,25 +4406,25 @@
     </x:row>
     <x:row r="40" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A40" s="12" t="s">
-        <x:v>683</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="B40" s="15" t="s">
-        <x:v>569</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C40" s="15" t="s">
-        <x:v>395</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
-        <x:v>352</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="G40" s="13" t="s">
-        <x:v>377</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H40" s="9"/>
       <x:c r="I40" s="9"/>
@@ -4340,25 +4435,25 @@
     </x:row>
     <x:row r="41" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A41" s="12" t="s">
-        <x:v>682</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="B41" s="15" t="s">
-        <x:v>274</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="C41" s="15" t="s">
-        <x:v>221</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
-        <x:v>484</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="G41" s="13" t="s">
-        <x:v>387</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="H41" s="9"/>
       <x:c r="I41" s="9"/>
@@ -4369,25 +4464,25 @@
     </x:row>
     <x:row r="42" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A42" s="12" t="s">
-        <x:v>701</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="B42" s="15" t="s">
-        <x:v>507</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="C42" s="15" t="s">
-        <x:v>406</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F42" s="12" t="s">
-        <x:v>473</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="G42" s="13" t="s">
-        <x:v>430</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="H42" s="9"/>
       <x:c r="I42" s="9"/>
@@ -4398,25 +4493,25 @@
     </x:row>
     <x:row r="43" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A43" s="12" t="s">
-        <x:v>685</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="B43" s="15" t="s">
-        <x:v>508</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="C43" s="15" t="s">
-        <x:v>220</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F43" s="12" t="s">
-        <x:v>464</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="G43" s="13" t="s">
-        <x:v>381</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H43" s="9"/>
       <x:c r="I43" s="9"/>
@@ -4427,25 +4522,25 @@
     </x:row>
     <x:row r="44" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A44" s="12" t="s">
-        <x:v>661</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="B44" s="15" t="s">
-        <x:v>289</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="C44" s="15" t="s">
-        <x:v>422</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D44" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F44" s="12" t="s">
-        <x:v>348</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="G44" s="13" t="s">
-        <x:v>374</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H44" s="9"/>
       <x:c r="I44" s="9"/>
@@ -4456,25 +4551,25 @@
     </x:row>
     <x:row r="45" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A45" s="12" t="s">
-        <x:v>687</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="B45" s="15" t="s">
-        <x:v>519</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="C45" s="15" t="s">
-        <x:v>404</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F45" s="12" t="s">
-        <x:v>347</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G45" s="13" t="s">
-        <x:v>443</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="H45" s="9"/>
       <x:c r="I45" s="9"/>
@@ -4485,25 +4580,25 @@
     </x:row>
     <x:row r="46" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A46" s="12" t="s">
-        <x:v>675</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="B46" s="15" t="s">
-        <x:v>276</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="C46" s="15" t="s">
-        <x:v>421</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D46" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E46" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F46" s="12" t="s">
-        <x:v>341</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="G46" s="13" t="s">
-        <x:v>437</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="H46" s="9"/>
       <x:c r="I46" s="9"/>
@@ -4514,25 +4609,25 @@
     </x:row>
     <x:row r="47" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A47" s="12" t="s">
-        <x:v>671</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="B47" s="15" t="s">
-        <x:v>514</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="C47" s="15" t="s">
-        <x:v>206</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D47" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
-        <x:v>475</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="G47" s="13" t="s">
-        <x:v>367</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H47" s="9"/>
       <x:c r="I47" s="9"/>
@@ -4543,25 +4638,25 @@
     </x:row>
     <x:row r="48" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A48" s="12" t="s">
-        <x:v>684</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>245</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C48" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D48" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E48" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F48" s="12" t="s">
-        <x:v>474</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="G48" s="13" t="s">
-        <x:v>438</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="H48" s="9"/>
       <x:c r="I48" s="9"/>
@@ -4572,25 +4667,25 @@
     </x:row>
     <x:row r="49" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A49" s="12" t="s">
-        <x:v>670</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
-        <x:v>580</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C49" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D49" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E49" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F49" s="12" t="s">
-        <x:v>333</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="G49" s="13" t="s">
-        <x:v>360</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="H49" s="9"/>
       <x:c r="I49" s="9"/>
@@ -4601,25 +4696,25 @@
     </x:row>
     <x:row r="50" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A50" s="12" t="s">
-        <x:v>148</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
-        <x:v>238</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C50" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D50" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E50" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F50" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G50" s="18" t="s">
-        <x:v>364</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H50" s="9"/>
       <x:c r="I50" s="9"/>
@@ -4630,25 +4725,25 @@
     </x:row>
     <x:row r="51" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A51" s="12" t="s">
-        <x:v>165</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
-        <x:v>304</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="C51" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D51" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E51" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F51" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G51" s="18" t="s">
-        <x:v>439</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="H51" s="9"/>
       <x:c r="I51" s="9"/>
@@ -4659,25 +4754,25 @@
     </x:row>
     <x:row r="52" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A52" s="12" t="s">
-        <x:v>144</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>290</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C52" s="12" t="s">
-        <x:v>405</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="D52" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E52" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G52" s="18" t="s">
-        <x:v>423</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="H52" s="9"/>
       <x:c r="I52" s="9"/>
@@ -4688,25 +4783,25 @@
     </x:row>
     <x:row r="53" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A53" s="12" t="s">
-        <x:v>152</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B53" s="12" t="s">
-        <x:v>241</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="C53" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D53" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E53" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F53" s="12" t="s">
-        <x:v>9</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G53" s="18" t="s">
-        <x:v>373</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H53" s="9"/>
       <x:c r="I53" s="9"/>
@@ -4717,25 +4812,25 @@
     </x:row>
     <x:row r="54" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A54" s="12" t="s">
-        <x:v>169</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B54" s="12" t="s">
-        <x:v>242</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C54" s="12" t="s">
-        <x:v>434</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="D54" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F54" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G54" s="18" t="s">
-        <x:v>309</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H54" s="9"/>
       <x:c r="I54" s="9"/>
@@ -4746,25 +4841,25 @@
     </x:row>
     <x:row r="55" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A55" s="12" t="s">
-        <x:v>173</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
-        <x:v>233</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="C55" s="12" t="s">
-        <x:v>30</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D55" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E55" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F55" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G55" s="18" t="s">
-        <x:v>370</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="H55" s="9"/>
       <x:c r="I55" s="9"/>
@@ -4775,25 +4870,25 @@
     </x:row>
     <x:row r="56" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A56" s="12" t="s">
-        <x:v>172</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B56" s="15" t="s">
-        <x:v>576</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C56" s="15" t="s">
-        <x:v>417</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F56" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G56" s="18" t="s">
-        <x:v>388</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="H56" s="9"/>
       <x:c r="I56" s="9"/>
@@ -4804,25 +4899,25 @@
     </x:row>
     <x:row r="57" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A57" s="12" t="s">
-        <x:v>161</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B57" s="15" t="s">
-        <x:v>509</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="C57" s="15" t="s">
-        <x:v>340</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D57" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E57" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F57" s="12" t="s">
-        <x:v>92</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G57" s="18" t="s">
-        <x:v>371</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H57" s="9"/>
       <x:c r="I57" s="9"/>
@@ -4833,25 +4928,25 @@
     </x:row>
     <x:row r="58" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A58" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
-        <x:v>524</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C58" s="12" t="s">
-        <x:v>710</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="D58" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E58" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F58" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G58" s="18" t="s">
-        <x:v>429</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="H58" s="9"/>
       <x:c r="I58" s="9"/>
@@ -4862,25 +4957,25 @@
     </x:row>
     <x:row r="59" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A59" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
-        <x:v>300</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C59" s="12" t="s">
-        <x:v>11</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D59" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E59" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F59" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G59" s="18" t="s">
-        <x:v>386</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="H59" s="9"/>
       <x:c r="I59" s="9"/>
@@ -4891,25 +4986,25 @@
     </x:row>
     <x:row r="60" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A60" s="12" t="s">
-        <x:v>133</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
-        <x:v>269</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="C60" s="12" t="s">
-        <x:v>662</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="D60" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E60" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F60" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G60" s="18" t="s">
-        <x:v>446</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="H60" s="9"/>
       <x:c r="I60" s="9"/>
@@ -4920,25 +5015,25 @@
     </x:row>
     <x:row r="61" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A61" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B61" s="12" t="s">
-        <x:v>307</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="C61" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D61" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E61" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F61" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G61" s="18" t="s">
-        <x:v>363</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H61" s="9"/>
       <x:c r="I61" s="9"/>
@@ -4949,25 +5044,25 @@
     </x:row>
     <x:row r="62" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A62" s="12" t="s">
-        <x:v>178</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
-        <x:v>250</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="C62" s="12" t="s">
-        <x:v>4</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D62" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E62" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F62" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G62" s="18" t="s">
-        <x:v>369</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H62" s="9"/>
       <x:c r="I62" s="9"/>
@@ -4978,25 +5073,25 @@
     </x:row>
     <x:row r="63" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A63" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B63" s="12" t="s">
-        <x:v>287</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="C63" s="12" t="s">
-        <x:v>653</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="D63" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E63" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F63" s="12" t="s">
-        <x:v>29</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G63" s="18" t="s">
-        <x:v>431</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="H63" s="9"/>
       <x:c r="I63" s="9"/>
@@ -5007,25 +5102,25 @@
     </x:row>
     <x:row r="64" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A64" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B64" s="12" t="s">
-        <x:v>236</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C64" s="12" t="s">
-        <x:v>681</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="D64" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E64" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F64" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G64" s="18" t="s">
-        <x:v>382</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="H64" s="9"/>
       <x:c r="I64" s="9"/>
@@ -5036,25 +5131,25 @@
     </x:row>
     <x:row r="65" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A65" s="12" t="s">
-        <x:v>140</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
-        <x:v>299</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="C65" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D65" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E65" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F65" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G65" s="18" t="s">
-        <x:v>419</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="H65" s="9"/>
       <x:c r="I65" s="9"/>
@@ -5065,25 +5160,25 @@
     </x:row>
     <x:row r="66" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A66" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B66" s="12" t="s">
-        <x:v>227</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C66" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D66" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E66" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F66" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G66" s="18" t="s">
-        <x:v>424</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="H66" s="9"/>
       <x:c r="I66" s="9"/>
@@ -5094,25 +5189,25 @@
     </x:row>
     <x:row r="67" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A67" s="12" t="s">
-        <x:v>156</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B67" s="12" t="s">
-        <x:v>535</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="C67" s="12" t="s">
-        <x:v>589</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="D67" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E67" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F67" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G67" s="18" t="s">
-        <x:v>440</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="H67" s="9"/>
       <x:c r="I67" s="9"/>
@@ -5123,25 +5218,25 @@
     </x:row>
     <x:row r="68" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A68" s="12" t="s">
-        <x:v>131</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B68" s="12" t="s">
-        <x:v>537</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="C68" s="12" t="s">
-        <x:v>102</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D68" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E68" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F68" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G68" s="18" t="s">
-        <x:v>372</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H68" s="9"/>
       <x:c r="I68" s="9"/>
@@ -5152,25 +5247,25 @@
     </x:row>
     <x:row r="69" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A69" s="12" t="s">
-        <x:v>125</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B69" s="15" t="s">
-        <x:v>568</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C69" s="15" t="s">
-        <x:v>216</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D69" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E69" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F69" s="12" t="s">
-        <x:v>18</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G69" s="18" t="s">
-        <x:v>385</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="H69" s="9"/>
       <x:c r="I69" s="9"/>
@@ -5181,25 +5276,25 @@
     </x:row>
     <x:row r="70" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A70" s="12" t="s">
-        <x:v>667</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="B70" s="15" t="s">
-        <x:v>511</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="C70" s="15" t="s">
-        <x:v>339</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="D70" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E70" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F70" s="12" t="s">
-        <x:v>457</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="G70" s="18" t="s">
-        <x:v>368</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H70" s="9"/>
       <x:c r="I70" s="9"/>
@@ -5210,25 +5305,25 @@
     </x:row>
     <x:row r="71" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A71" s="12" t="s">
-        <x:v>698</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B71" s="12" t="s">
-        <x:v>540</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="C71" s="15" t="s">
-        <x:v>442</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="D71" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E71" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F71" s="12" t="s">
-        <x:v>345</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="G71" s="18" t="s">
-        <x:v>432</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="H71" s="9"/>
       <x:c r="I71" s="9"/>
@@ -5239,25 +5334,25 @@
     </x:row>
     <x:row r="72" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A72" s="12" t="s">
-        <x:v>696</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B72" s="15" t="s">
-        <x:v>579</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C72" s="15" t="s">
-        <x:v>420</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D72" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E72" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F72" s="12" t="s">
-        <x:v>319</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G72" s="18" t="s">
-        <x:v>427</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="H72" s="9"/>
       <x:c r="I72" s="9"/>
@@ -5268,25 +5363,25 @@
     </x:row>
     <x:row r="73" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A73" s="12" t="s">
-        <x:v>691</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B73" s="15" t="s">
-        <x:v>561</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="C73" s="15" t="s">
-        <x:v>349</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="D73" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E73" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F73" s="12" t="s">
-        <x:v>493</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="G73" s="18" t="s">
-        <x:v>435</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="H73" s="9"/>
       <x:c r="I73" s="9"/>
@@ -5297,25 +5392,25 @@
     </x:row>
     <x:row r="74" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A74" s="12" t="s">
-        <x:v>748</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B74" s="15" t="s">
-        <x:v>192</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C74" s="15" t="s">
-        <x:v>396</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D74" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E74" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F74" s="12" t="s">
-        <x:v>480</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="G74" s="18" t="s">
-        <x:v>376</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H74" s="9"/>
       <x:c r="I74" s="9"/>
@@ -5326,48 +5421,48 @@
     </x:row>
     <x:row r="75" spans="1:7" s="9" customFormat="1" customHeight="1">
       <x:c r="A75" s="10" t="s">
-        <x:v>146</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B75" s="10" t="s">
-        <x:v>549</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="C75" s="10" t="s">
-        <x:v>582</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="D75" s="10" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E75" s="10" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F75" s="10" t="s">
-        <x:v>81</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G75" s="10" t="s">
-        <x:v>458</x:v>
+        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A76" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B76" s="12" t="s">
-        <x:v>522</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="C76" s="12" t="s">
-        <x:v>655</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="D76" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E76" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F76" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G76" s="12" t="s">
-        <x:v>462</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="H76" s="9"/>
       <x:c r="I76" s="9"/>
@@ -5378,25 +5473,25 @@
     </x:row>
     <x:row r="77" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A77" s="12" t="s">
-        <x:v>157</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B77" s="12" t="s">
-        <x:v>225</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C77" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D77" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E77" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F77" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G77" s="12" t="s">
-        <x:v>488</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="H77" s="9"/>
       <x:c r="I77" s="9"/>
@@ -5407,25 +5502,25 @@
     </x:row>
     <x:row r="78" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A78" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B78" s="12" t="s">
-        <x:v>234</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C78" s="12" t="s">
-        <x:v>344</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D78" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E78" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F78" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G78" s="12" t="s">
-        <x:v>460</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="H78" s="9"/>
       <x:c r="I78" s="9"/>
@@ -5436,25 +5531,25 @@
     </x:row>
     <x:row r="79" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A79" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B79" s="12" t="s">
-        <x:v>235</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="C79" s="12" t="s">
-        <x:v>649</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="D79" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E79" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F79" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G79" s="12" t="s">
-        <x:v>343</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="H79" s="9"/>
       <x:c r="I79" s="9"/>
@@ -5465,25 +5560,25 @@
     </x:row>
     <x:row r="80" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A80" s="12" t="s">
-        <x:v>180</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B80" s="12" t="s">
-        <x:v>229</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C80" s="12" t="s">
-        <x:v>725</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D80" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E80" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F80" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G80" s="12" t="s">
-        <x:v>476</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="H80" s="9"/>
       <x:c r="I80" s="9"/>
@@ -5494,25 +5589,25 @@
     </x:row>
     <x:row r="81" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A81" s="12" t="s">
-        <x:v>160</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B81" s="12" t="s">
-        <x:v>225</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C81" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D81" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E81" s="12" t="s">
-        <x:v>303</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F81" s="12" t="s">
-        <x:v>35</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G81" s="12" t="s">
-        <x:v>459</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="H81" s="9"/>
       <x:c r="I81" s="9"/>
@@ -5523,25 +5618,25 @@
     </x:row>
     <x:row r="82" spans="1:13" s="14" customFormat="1" customHeight="1">
       <x:c r="A82" s="16" t="s">
-        <x:v>713</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="B82" s="19" t="s">
-        <x:v>0</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C82" s="19" t="s">
-        <x:v>1</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D82" s="16" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E82" s="16" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F82" s="16" t="s">
-        <x:v>356</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="G82" s="16" t="s">
-        <x:v>217</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H82" s="9"/>
       <x:c r="I82" s="9"/>
@@ -5552,71 +5647,71 @@
     </x:row>
     <x:row r="83" spans="1:7" s="9" customFormat="1" customHeight="1">
       <x:c r="A83" s="10" t="s">
-        <x:v>741</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="B83" s="18" t="s">
-        <x:v>104</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C83" s="18" t="s">
-        <x:v>767</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="D83" s="10" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E83" s="10" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F83" s="10" t="s">
-        <x:v>461</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="G83" s="10" t="s">
-        <x:v>205</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7" s="9" customFormat="1" customHeight="1">
       <x:c r="A84" s="10" t="s">
-        <x:v>714</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="B84" s="10" t="s">
-        <x:v>305</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C84" s="10" t="s">
-        <x:v>389</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D84" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E84" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F84" s="12" t="s">
-        <x:v>489</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="G84" s="12" t="s">
-        <x:v>218</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A85" s="12" t="s">
-        <x:v>716</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B85" s="18" t="s">
-        <x:v>103</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C85" s="18" t="s">
-        <x:v>763</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="D85" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E85" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F85" s="12" t="s">
-        <x:v>451</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="G85" s="12" t="s">
-        <x:v>208</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H85" s="9"/>
       <x:c r="I85" s="9"/>
@@ -5627,25 +5722,25 @@
     </x:row>
     <x:row r="86" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A86" s="12" t="s">
-        <x:v>715</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="B86" s="18" t="s">
-        <x:v>244</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C86" s="18" t="s">
-        <x:v>769</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="D86" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E86" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F86" s="12" t="s">
-        <x:v>455</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="G86" s="12" t="s">
-        <x:v>204</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H86" s="9"/>
       <x:c r="I86" s="9"/>
@@ -5656,25 +5751,25 @@
     </x:row>
     <x:row r="87" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A87" s="12" t="s">
-        <x:v>693</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="B87" s="12" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="C87" s="12" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D87" s="12" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="E87" s="12" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="F87" s="12" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="G87" s="12" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="C87" s="12" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D87" s="12" t="s">
-        <x:v>578</x:v>
-      </x:c>
-      <x:c r="E87" s="12" t="s">
-        <x:v>533</x:v>
-      </x:c>
-      <x:c r="F87" s="12" t="s">
-        <x:v>465</x:v>
-      </x:c>
-      <x:c r="G87" s="12" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="H87" s="9"/>
       <x:c r="I87" s="9"/>
@@ -5685,25 +5780,25 @@
     </x:row>
     <x:row r="88" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A88" s="12" t="s">
-        <x:v>705</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="B88" s="12" t="s">
-        <x:v>223</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="C88" s="12" t="s">
-        <x:v>346</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D88" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E88" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F88" s="12" t="s">
-        <x:v>468</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="G88" s="12" t="s">
-        <x:v>211</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="H88" s="9"/>
       <x:c r="I88" s="9"/>
@@ -5714,25 +5809,25 @@
     </x:row>
     <x:row r="89" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A89" s="12" t="s">
-        <x:v>718</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B89" s="18" t="s">
-        <x:v>105</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C89" s="18" t="s">
-        <x:v>765</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D89" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E89" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F89" s="12" t="s">
-        <x:v>329</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="G89" s="12" t="s">
-        <x:v>202</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H89" s="9"/>
       <x:c r="I89" s="9"/>
@@ -5743,25 +5838,25 @@
     </x:row>
     <x:row r="90" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A90" s="12" t="s">
-        <x:v>697</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="B90" s="12" t="s">
-        <x:v>298</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="C90" s="12" t="s">
-        <x:v>313</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D90" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E90" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F90" s="12" t="s">
-        <x:v>321</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G90" s="12" t="s">
-        <x:v>203</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H90" s="9"/>
       <x:c r="I90" s="9"/>
@@ -5772,25 +5867,25 @@
     </x:row>
     <x:row r="91" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A91" s="12" t="s">
-        <x:v>707</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="B91" s="12" t="s">
-        <x:v>295</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C91" s="12" t="s">
-        <x:v>472</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="D91" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E91" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F91" s="12" t="s">
-        <x:v>332</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G91" s="12" t="s">
-        <x:v>215</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H91" s="9"/>
       <x:c r="I91" s="9"/>
@@ -5801,25 +5896,25 @@
     </x:row>
     <x:row r="92" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A92" s="12" t="s">
-        <x:v>750</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="B92" s="18" t="s">
-        <x:v>768</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="C92" s="18" t="s">
-        <x:v>2</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="D92" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E92" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F92" s="12" t="s">
-        <x:v>448</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="G92" s="12" t="s">
-        <x:v>207</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="H92" s="9"/>
       <x:c r="I92" s="9"/>
@@ -5830,25 +5925,25 @@
     </x:row>
     <x:row r="93" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A93" s="12" t="s">
-        <x:v>709</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="B93" s="18" t="s">
-        <x:v>761</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C93" s="18" t="s">
-        <x:v>766</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="D93" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E93" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F93" s="12" t="s">
-        <x:v>351</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="G93" s="12" t="s">
-        <x:v>214</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H93" s="9"/>
       <x:c r="I93" s="9"/>
@@ -5859,25 +5954,25 @@
     </x:row>
     <x:row r="94" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A94" s="12" t="s">
-        <x:v>708</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="B94" s="18" t="s">
-        <x:v>762</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C94" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="D94" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E94" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F94" s="12" t="s">
-        <x:v>466</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="G94" s="12" t="s">
-        <x:v>209</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H94" s="9"/>
       <x:c r="I94" s="9"/>
@@ -5888,25 +5983,25 @@
     </x:row>
     <x:row r="95" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A95" s="12" t="s">
-        <x:v>703</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="B95" s="18" t="s">
-        <x:v>106</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="C95" s="18" t="s">
-        <x:v>764</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="D95" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E95" s="12" t="s">
-        <x:v>533</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="F95" s="12" t="s">
-        <x:v>470</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="G95" s="12" t="s">
-        <x:v>200</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="H95" s="9"/>
       <x:c r="I95" s="9"/>
@@ -5917,25 +6012,25 @@
     </x:row>
     <x:row r="96" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A96" s="16" t="s">
-        <x:v>167</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B96" s="16" t="s">
-        <x:v>239</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C96" s="16" t="s">
-        <x:v>692</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="D96" s="16" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E96" s="16" t="s">
-        <x:v>302</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F96" s="16" t="s">
-        <x:v>80</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G96" s="16" t="s">
-        <x:v>403</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="H96" s="9"/>
       <x:c r="I96" s="9"/>
@@ -5946,25 +6041,25 @@
     </x:row>
     <x:row r="97" spans="1:13" s="14" customFormat="1" customHeight="1">
       <x:c r="A97" s="12" t="s">
-        <x:v>162</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B97" s="12" t="s">
-        <x:v>243</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="C97" s="12" t="s">
-        <x:v>596</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="D97" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E97" s="12" t="s">
-        <x:v>302</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F97" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G97" s="12" t="s">
-        <x:v>409</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="H97" s="20"/>
       <x:c r="I97" s="20"/>
@@ -5975,25 +6070,25 @@
     </x:row>
     <x:row r="98" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A98" s="12" t="s">
-        <x:v>153</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B98" s="12" t="s">
-        <x:v>308</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C98" s="12" t="s">
-        <x:v>723</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="D98" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E98" s="12" t="s">
-        <x:v>302</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F98" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G98" s="12" t="s">
-        <x:v>412</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="H98" s="9"/>
       <x:c r="I98" s="9"/>
@@ -6004,25 +6099,25 @@
     </x:row>
     <x:row r="99" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A99" s="12" t="s">
-        <x:v>120</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B99" s="12" t="s">
-        <x:v>297</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="C99" s="12" t="s">
-        <x:v>694</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="D99" s="12" t="s">
-        <x:v>578</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="E99" s="12" t="s">
-        <x:v>302</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F99" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G99" s="12" t="s">
-        <x:v>416</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="H99" s="9"/>
       <x:c r="I99" s="9"/>
@@ -6033,25 +6128,25 @@
     </x:row>
     <x:row r="100" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A100" s="16" t="s">
-        <x:v>734</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="B100" s="16" t="s">
-        <x:v>249</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="C100" s="16" t="s">
-        <x:v>695</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="D100" s="16" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E100" s="16" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F100" s="16" t="s">
-        <x:v>607</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="G100" s="16" t="s">
-        <x:v>436</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="H100" s="9"/>
       <x:c r="I100" s="9"/>
@@ -6062,25 +6157,25 @@
     </x:row>
     <x:row r="101" spans="1:13" s="14" customFormat="1" customHeight="1">
       <x:c r="A101" s="12" t="s">
-        <x:v>712</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="B101" s="12" t="s">
-        <x:v>231</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="C101" s="12" t="s">
-        <x:v>631</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="D101" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E101" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F101" s="12" t="s">
-        <x:v>624</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="G101" s="12" t="s">
-        <x:v>428</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="H101" s="9"/>
       <x:c r="I101" s="9"/>
@@ -6091,25 +6186,25 @@
     </x:row>
     <x:row r="102" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A102" s="12" t="s">
-        <x:v>731</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="B102" s="12" t="s">
-        <x:v>254</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="C102" s="12" t="s">
-        <x:v>623</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="D102" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E102" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F102" s="12" t="s">
-        <x:v>616</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="G102" s="12" t="s">
-        <x:v>392</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="H102" s="9"/>
       <x:c r="I102" s="9"/>
@@ -6120,25 +6215,25 @@
     </x:row>
     <x:row r="103" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A103" s="12" t="s">
-        <x:v>700</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="B103" s="12" t="s">
-        <x:v>257</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="C103" s="12" t="s">
-        <x:v>36</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D103" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E103" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F103" s="12" t="s">
-        <x:v>635</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="G103" s="12" t="s">
-        <x:v>399</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="H103" s="9"/>
       <x:c r="I103" s="9"/>
@@ -6149,25 +6244,25 @@
     </x:row>
     <x:row r="104" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A104" s="12" t="s">
-        <x:v>717</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="B104" s="12" t="s">
-        <x:v>532</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C104" s="12" t="s">
-        <x:v>483</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="D104" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E104" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F104" s="12" t="s">
-        <x:v>613</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="G104" s="12" t="s">
-        <x:v>418</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="H104" s="9"/>
       <x:c r="I104" s="9"/>
@@ -6178,25 +6273,25 @@
     </x:row>
     <x:row r="105" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A105" s="12" t="s">
-        <x:v>704</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="B105" s="12" t="s">
-        <x:v>278</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="C105" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D105" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E105" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F105" s="12" t="s">
-        <x:v>612</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="G105" s="12" t="s">
-        <x:v>433</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="H105" s="9"/>
       <x:c r="I105" s="9"/>
@@ -6207,25 +6302,25 @@
     </x:row>
     <x:row r="106" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A106" s="12" t="s">
-        <x:v>690</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="B106" s="12" t="s">
-        <x:v>265</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C106" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D106" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E106" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F106" s="12" t="s">
-        <x:v>620</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="G106" s="12" t="s">
-        <x:v>444</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="H106" s="9"/>
       <x:c r="I106" s="9"/>
@@ -6236,25 +6331,25 @@
     </x:row>
     <x:row r="107" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A107" s="12" t="s">
-        <x:v>749</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="B107" s="12" t="s">
-        <x:v>523</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="C107" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D107" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E107" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F107" s="12" t="s">
-        <x:v>614</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="G107" s="12" t="s">
-        <x:v>391</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="H107" s="9"/>
       <x:c r="I107" s="9"/>
@@ -6265,25 +6360,25 @@
     </x:row>
     <x:row r="108" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A108" s="12" t="s">
-        <x:v>735</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="B108" s="12" t="s">
-        <x:v>528</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="C108" s="12" t="s">
-        <x:v>627</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="D108" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E108" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F108" s="12" t="s">
-        <x:v>637</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="G108" s="12" t="s">
-        <x:v>398</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="H108" s="9"/>
       <x:c r="I108" s="9"/>
@@ -6294,25 +6389,25 @@
     </x:row>
     <x:row r="109" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A109" s="12" t="s">
-        <x:v>739</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="B109" s="12" t="s">
-        <x:v>251</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="C109" s="12" t="s">
-        <x:v>659</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="D109" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E109" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F109" s="12" t="s">
-        <x:v>643</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="G109" s="12" t="s">
-        <x:v>400</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="H109" s="9"/>
       <x:c r="I109" s="9"/>
@@ -6323,25 +6418,25 @@
     </x:row>
     <x:row r="110" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A110" s="12" t="s">
-        <x:v>751</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="B110" s="12" t="s">
-        <x:v>264</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C110" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D110" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E110" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F110" s="12" t="s">
-        <x:v>619</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="G110" s="12" t="s">
-        <x:v>401</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="H110" s="9"/>
       <x:c r="I110" s="9"/>
@@ -6352,25 +6447,25 @@
     </x:row>
     <x:row r="111" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A111" s="12" t="s">
-        <x:v>728</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="B111" s="12" t="s">
-        <x:v>271</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="C111" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D111" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E111" s="12" t="s">
-        <x:v>277</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F111" s="12" t="s">
-        <x:v>640</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="G111" s="12" t="s">
-        <x:v>426</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="H111" s="9"/>
       <x:c r="I111" s="9"/>
@@ -6381,25 +6476,25 @@
     </x:row>
     <x:row r="112" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A112" s="16" t="s">
-        <x:v>747</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="B112" s="16" t="s">
-        <x:v>279</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C112" s="16" t="s">
-        <x:v>174</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D112" s="16" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E112" s="16" t="s">
-        <x:v>224</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F112" s="16" t="s">
-        <x:v>657</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="G112" s="16" t="s">
-        <x:v>390</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="H112" s="9"/>
       <x:c r="I112" s="9"/>
@@ -6410,25 +6505,25 @@
     </x:row>
     <x:row r="113" spans="1:13" s="14" customFormat="1" customHeight="1">
       <x:c r="A113" s="12" t="s">
-        <x:v>754</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="B113" s="12" t="s">
-        <x:v>246</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C113" s="12" t="s">
-        <x:v>756</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="D113" s="12" t="s">
-        <x:v>270</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E113" s="12" t="s">
-        <x:v>224</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F113" s="12" t="s">
-        <x:v>609</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="G113" s="12" t="s">
-        <x:v>394</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="H113" s="9"/>
       <x:c r="I113" s="9"/>
@@ -6439,25 +6534,25 @@
     </x:row>
     <x:row r="114" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A114" s="16" t="s">
-        <x:v>198</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B114" s="16" t="s">
-        <x:v>261</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="C114" s="16" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D114" s="16" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E114" s="16" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F114" s="16" t="s">
-        <x:v>621</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="G114" s="16" t="s">
-        <x:v>42</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H114" s="9"/>
       <x:c r="I114" s="9"/>
@@ -6468,25 +6563,25 @@
     </x:row>
     <x:row r="115" spans="1:13" s="14" customFormat="1" customHeight="1">
       <x:c r="A115" s="12" t="s">
-        <x:v>195</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B115" s="12" t="s">
-        <x:v>247</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="C115" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D115" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E115" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F115" s="12" t="s">
-        <x:v>632</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="G115" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H115" s="9"/>
       <x:c r="I115" s="9"/>
@@ -6497,25 +6592,25 @@
     </x:row>
     <x:row r="116" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A116" s="12" t="s">
-        <x:v>194</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B116" s="12" t="s">
-        <x:v>255</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="C116" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D116" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E116" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F116" s="12" t="s">
-        <x:v>626</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G116" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H116" s="9"/>
       <x:c r="I116" s="9"/>
@@ -6526,25 +6621,25 @@
     </x:row>
     <x:row r="117" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A117" s="12" t="s">
-        <x:v>184</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B117" s="12" t="s">
-        <x:v>551</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="C117" s="12" t="s">
-        <x:v>454</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="D117" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E117" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F117" s="12" t="s">
-        <x:v>629</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="G117" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H117" s="9"/>
       <x:c r="I117" s="9"/>
@@ -6555,25 +6650,25 @@
     </x:row>
     <x:row r="118" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A118" s="12" t="s">
-        <x:v>186</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B118" s="12" t="s">
-        <x:v>284</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C118" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D118" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E118" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F118" s="12" t="s">
-        <x:v>634</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="G118" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H118" s="9"/>
       <x:c r="I118" s="9"/>
@@ -6584,25 +6679,25 @@
     </x:row>
     <x:row r="119" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A119" s="12" t="s">
-        <x:v>196</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B119" s="12" t="s">
-        <x:v>530</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="C119" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D119" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E119" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F119" s="12" t="s">
-        <x:v>628</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="G119" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H119" s="9"/>
       <x:c r="I119" s="9"/>
@@ -6613,25 +6708,25 @@
     </x:row>
     <x:row r="120" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A120" s="12" t="s">
-        <x:v>190</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B120" s="12" t="s">
-        <x:v>199</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C120" s="12" t="s">
-        <x:v>452</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="D120" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E120" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F120" s="12" t="s">
-        <x:v>644</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="G120" s="12" t="s">
-        <x:v>41</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H120" s="9"/>
       <x:c r="I120" s="9"/>
@@ -6642,25 +6737,25 @@
     </x:row>
     <x:row r="121" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A121" s="12" t="s">
-        <x:v>187</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B121" s="12" t="s">
-        <x:v>541</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="C121" s="12" t="s">
-        <x:v>494</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D121" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E121" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F121" s="12" t="s">
-        <x:v>633</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="G121" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H121" s="9"/>
       <x:c r="I121" s="9"/>
@@ -6671,25 +6766,25 @@
     </x:row>
     <x:row r="122" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A122" s="12" t="s">
-        <x:v>197</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B122" s="12" t="s">
-        <x:v>240</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C122" s="12" t="s">
-        <x:v>39</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D122" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E122" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F122" s="12" t="s">
-        <x:v>630</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="G122" s="12" t="s">
-        <x:v>353</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="H122" s="9"/>
       <x:c r="I122" s="9"/>
@@ -6700,25 +6795,25 @@
     </x:row>
     <x:row r="123" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A123" s="12" t="s">
-        <x:v>193</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B123" s="12" t="s">
-        <x:v>273</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C123" s="12" t="s">
-        <x:v>453</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="D123" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E123" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F123" s="12" t="s">
-        <x:v>638</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="G123" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H123" s="9"/>
       <x:c r="I123" s="9"/>
@@ -6729,25 +6824,25 @@
     </x:row>
     <x:row r="124" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A124" s="12" t="s">
-        <x:v>138</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B124" s="12" t="s">
-        <x:v>510</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="C124" s="12" t="s">
-        <x:v>402</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="D124" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E124" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F124" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G124" s="12" t="s">
-        <x:v>415</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="H124" s="9"/>
       <x:c r="I124" s="9"/>
@@ -6758,25 +6853,25 @@
     </x:row>
     <x:row r="125" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A125" s="12" t="s">
-        <x:v>654</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="B125" s="12" t="s">
-        <x:v>497</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C125" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D125" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E125" s="12" t="s">
-        <x:v>232</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F125" s="12" t="s">
-        <x:v>410</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="G125" s="12" t="s">
-        <x:v>212</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H125" s="9"/>
       <x:c r="I125" s="9"/>
@@ -6787,25 +6882,25 @@
     </x:row>
     <x:row r="126" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A126" s="16" t="s">
-        <x:v>191</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B126" s="16" t="s">
-        <x:v>230</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="C126" s="16" t="s">
-        <x:v>758</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="D126" s="16" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E126" s="16" t="s">
-        <x:v>546</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F126" s="16" t="s">
-        <x:v>652</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="G126" s="16" t="s">
-        <x:v>490</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="H126" s="9"/>
       <x:c r="I126" s="9"/>
@@ -6816,25 +6911,25 @@
     </x:row>
     <x:row r="127" spans="1:13" s="14" customFormat="1" customHeight="1">
       <x:c r="A127" s="12" t="s">
-        <x:v>721</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="B127" s="12" t="s">
-        <x:v>291</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="C127" s="12" t="s">
-        <x:v>645</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="D127" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E127" s="12" t="s">
-        <x:v>546</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F127" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G127" s="12" t="s">
-        <x:v>425</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="H127" s="9"/>
       <x:c r="I127" s="9"/>
@@ -6845,25 +6940,25 @@
     </x:row>
     <x:row r="128" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A128" s="12" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B128" s="12" t="s">
-        <x:v>268</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C128" s="12" t="s">
-        <x:v>143</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D128" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E128" s="12" t="s">
-        <x:v>546</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F128" s="12" t="s">
-        <x:v>586</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="G128" s="12" t="s">
-        <x:v>486</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="H128" s="9"/>
       <x:c r="I128" s="9"/>
@@ -6874,25 +6969,25 @@
     </x:row>
     <x:row r="129" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A129" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B129" s="12" t="s">
-        <x:v>260</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C129" s="12" t="s">
-        <x:v>122</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D129" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E129" s="12" t="s">
-        <x:v>546</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F129" s="12" t="s">
-        <x:v>595</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="G129" s="12" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="H129" s="9"/>
       <x:c r="I129" s="9"/>
@@ -6903,25 +6998,25 @@
     </x:row>
     <x:row r="130" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A130" s="12" t="s">
-        <x:v>746</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B130" s="12" t="s">
-        <x:v>266</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C130" s="12" t="s">
-        <x:v>726</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="D130" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E130" s="12" t="s">
-        <x:v>546</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F130" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G130" s="12" t="s">
-        <x:v>445</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="H130" s="9"/>
       <x:c r="I130" s="9"/>
@@ -6932,25 +7027,25 @@
     </x:row>
     <x:row r="131" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A131" s="12" t="s">
-        <x:v>163</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B131" s="12" t="s">
-        <x:v>301</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C131" s="12" t="s">
-        <x:v>636</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D131" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E131" s="12" t="s">
-        <x:v>546</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="F131" s="12" t="s">
-        <x:v>34</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G131" s="12" t="s">
-        <x:v>471</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="H131" s="9"/>
       <x:c r="I131" s="9"/>
@@ -6960,26 +7055,26 @@
       <x:c r="M131" s="9"/>
     </x:row>
     <x:row r="132" spans="1:13" s="11" customFormat="1" customHeight="1">
-      <x:c r="A132" s="16" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="B132" s="16" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="C132" s="16" t="s">
-        <x:v>752</x:v>
-      </x:c>
-      <x:c r="D132" s="16" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="E132" s="16" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F132" s="16" t="s">
-        <x:v>722</x:v>
-      </x:c>
-      <x:c r="G132" s="16" t="s">
-        <x:v>54</x:v>
+      <x:c r="A132" s="12" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B132" s="12" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C132" s="12" t="s">
+        <x:v>787</x:v>
+      </x:c>
+      <x:c r="D132" s="12" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E132" s="12" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="F132" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G132" s="12" t="s">
+        <x:v>789</x:v>
       </x:c>
       <x:c r="H132" s="9"/>
       <x:c r="I132" s="9"/>
@@ -6988,27 +7083,27 @@
       <x:c r="L132" s="9"/>
       <x:c r="M132" s="9"/>
     </x:row>
-    <x:row r="133" spans="1:13" s="14" customFormat="1" customHeight="1">
-      <x:c r="A133" s="12" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="B133" s="12" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C133" s="12" t="s">
-        <x:v>742</x:v>
-      </x:c>
-      <x:c r="D133" s="12" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="E133" s="12" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F133" s="12" t="s">
-        <x:v>585</x:v>
-      </x:c>
-      <x:c r="G133" s="12" t="s">
-        <x:v>64</x:v>
+    <x:row r="133" spans="1:13" s="11" customFormat="1" customHeight="1">
+      <x:c r="A133" s="16" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B133" s="16" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="C133" s="16" t="s">
+        <x:v>747</x:v>
+      </x:c>
+      <x:c r="D133" s="16" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E133" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F133" s="16" t="s">
+        <x:v>773</x:v>
+      </x:c>
+      <x:c r="G133" s="16" t="s">
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H133" s="9"/>
       <x:c r="I133" s="9"/>
@@ -7017,27 +7112,27 @@
       <x:c r="L133" s="9"/>
       <x:c r="M133" s="9"/>
     </x:row>
-    <x:row r="134" spans="1:13" s="11" customFormat="1" customHeight="1">
+    <x:row r="134" spans="1:13" s="14" customFormat="1" customHeight="1">
       <x:c r="A134" s="12" t="s">
-        <x:v>577</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B134" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C134" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="D134" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E134" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F134" s="12" t="s">
-        <x:v>724</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="G134" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H134" s="9"/>
       <x:c r="I134" s="9"/>
@@ -7048,25 +7143,25 @@
     </x:row>
     <x:row r="135" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A135" s="12" t="s">
-        <x:v>559</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B135" s="12" t="s">
-        <x:v>285</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C135" s="12" t="s">
-        <x:v>744</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D135" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E135" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F135" s="12" t="s">
-        <x:v>720</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="G135" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H135" s="9"/>
       <x:c r="I135" s="9"/>
@@ -7077,25 +7172,25 @@
     </x:row>
     <x:row r="136" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A136" s="12" t="s">
-        <x:v>558</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B136" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="C136" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="D136" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E136" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F136" s="12" t="s">
-        <x:v>737</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="G136" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H136" s="9"/>
       <x:c r="I136" s="9"/>
@@ -7106,25 +7201,25 @@
     </x:row>
     <x:row r="137" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A137" s="12" t="s">
-        <x:v>553</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B137" s="12" t="s">
-        <x:v>258</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C137" s="12" t="s">
-        <x:v>647</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="D137" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E137" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F137" s="12" t="s">
-        <x:v>753</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="G137" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H137" s="9"/>
       <x:c r="I137" s="9"/>
@@ -7135,25 +7230,25 @@
     </x:row>
     <x:row r="138" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A138" s="12" t="s">
-        <x:v>573</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B138" s="12" t="s">
-        <x:v>263</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C138" s="12" t="s">
-        <x:v>651</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="D138" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E138" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F138" s="12" t="s">
-        <x:v>730</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="G138" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H138" s="9"/>
       <x:c r="I138" s="9"/>
@@ -7164,25 +7259,25 @@
     </x:row>
     <x:row r="139" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A139" s="12" t="s">
-        <x:v>567</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B139" s="12" t="s">
-        <x:v>275</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C139" s="12" t="s">
-        <x:v>447</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="D139" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E139" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F139" s="12" t="s">
-        <x:v>736</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="G139" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H139" s="9"/>
       <x:c r="I139" s="9"/>
@@ -7192,26 +7287,26 @@
       <x:c r="M139" s="9"/>
     </x:row>
     <x:row r="140" spans="1:13" s="11" customFormat="1" customHeight="1">
-      <x:c r="A140" s="16" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="B140" s="16" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="C140" s="16" t="s">
-        <x:v>743</x:v>
-      </x:c>
-      <x:c r="D140" s="16" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="E140" s="16" t="s">
-        <x:v>556</x:v>
-      </x:c>
-      <x:c r="F140" s="16" t="s">
-        <x:v>602</x:v>
-      </x:c>
-      <x:c r="G140" s="16" t="s">
-        <x:v>487</x:v>
+      <x:c r="A140" s="12" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B140" s="12" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="C140" s="12" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="D140" s="12" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E140" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F140" s="12" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="G140" s="12" t="s">
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H140" s="9"/>
       <x:c r="I140" s="9"/>
@@ -7220,27 +7315,27 @@
       <x:c r="L140" s="9"/>
       <x:c r="M140" s="9"/>
     </x:row>
-    <x:row r="141" spans="1:13" s="14" customFormat="1" customHeight="1">
+    <x:row r="141" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A141" s="12" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="B141" s="12" t="s">
-        <x:v>288</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B141" s="18" t="s">
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C141" s="12" t="s">
-        <x:v>658</x:v>
-      </x:c>
-      <x:c r="D141" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D141" s="18" t="s">
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E141" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F141" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="G141" s="12" t="s">
-        <x:v>407</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="H141" s="9"/>
       <x:c r="I141" s="9"/>
@@ -7251,25 +7346,25 @@
     </x:row>
     <x:row r="142" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A142" s="12" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="B142" s="12" t="s">
-        <x:v>555</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B142" s="18" t="s">
+        <x:v>793</x:v>
       </x:c>
       <x:c r="C142" s="12" t="s">
-        <x:v>738</x:v>
-      </x:c>
-      <x:c r="D142" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D142" s="18" t="s">
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E142" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F142" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="G142" s="12" t="s">
-        <x:v>397</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="H142" s="9"/>
       <x:c r="I142" s="9"/>
@@ -7280,25 +7375,25 @@
     </x:row>
     <x:row r="143" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A143" s="12" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="B143" s="12" t="s">
-        <x:v>272</x:v>
+        <x:v>790</x:v>
+      </x:c>
+      <x:c r="B143" s="18" t="s">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C143" s="12" t="s">
-        <x:v>733</x:v>
-      </x:c>
-      <x:c r="D143" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D143" s="18" t="s">
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E143" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F143" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="G143" s="12" t="s">
-        <x:v>393</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="H143" s="9"/>
       <x:c r="I143" s="9"/>
@@ -7309,25 +7404,25 @@
     </x:row>
     <x:row r="144" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A144" s="12" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="B144" s="12" t="s">
-        <x:v>282</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B144" s="18" t="s">
+        <x:v>788</x:v>
       </x:c>
       <x:c r="C144" s="12" t="s">
-        <x:v>732</x:v>
-      </x:c>
-      <x:c r="D144" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>787</x:v>
+      </x:c>
+      <x:c r="D144" s="18" t="s">
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E144" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F144" s="12" t="s">
-        <x:v>592</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G144" s="12" t="s">
-        <x:v>485</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="H144" s="9"/>
       <x:c r="I144" s="9"/>
@@ -7337,26 +7432,26 @@
       <x:c r="M144" s="9"/>
     </x:row>
     <x:row r="145" spans="1:13" s="11" customFormat="1" customHeight="1">
-      <x:c r="A145" s="12" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="B145" s="12" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="C145" s="12" t="s">
-        <x:v>729</x:v>
-      </x:c>
-      <x:c r="D145" s="12" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="E145" s="12" t="s">
-        <x:v>556</x:v>
-      </x:c>
-      <x:c r="F145" s="12" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="G145" s="12" t="s">
-        <x:v>65</x:v>
+      <x:c r="A145" s="16" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B145" s="16" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="C145" s="16" t="s">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="D145" s="16" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E145" s="16" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="F145" s="16" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="G145" s="16" t="s">
+        <x:v>345</x:v>
       </x:c>
       <x:c r="H145" s="9"/>
       <x:c r="I145" s="9"/>
@@ -7365,27 +7460,27 @@
       <x:c r="L145" s="9"/>
       <x:c r="M145" s="9"/>
     </x:row>
-    <x:row r="146" spans="1:13" s="11" customFormat="1" customHeight="1">
+    <x:row r="146" spans="1:13" s="14" customFormat="1" customHeight="1">
       <x:c r="A146" s="12" t="s">
-        <x:v>572</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B146" s="12" t="s">
-        <x:v>281</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="C146" s="12" t="s">
-        <x:v>727</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="D146" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E146" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F146" s="12" t="s">
-        <x:v>711</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G146" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="H146" s="9"/>
       <x:c r="I146" s="9"/>
@@ -7396,25 +7491,25 @@
     </x:row>
     <x:row r="147" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A147" s="12" t="s">
-        <x:v>554</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B147" s="12" t="s">
-        <x:v>557</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="C147" s="12" t="s">
-        <x:v>597</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="D147" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E147" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F147" s="12" t="s">
-        <x:v>757</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G147" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="H147" s="9"/>
       <x:c r="I147" s="9"/>
@@ -7425,25 +7520,25 @@
     </x:row>
     <x:row r="148" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A148" s="12" t="s">
-        <x:v>548</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B148" s="12" t="s">
-        <x:v>306</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C148" s="12" t="s">
-        <x:v>639</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="D148" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E148" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F148" s="12" t="s">
-        <x:v>719</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G148" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="H148" s="9"/>
       <x:c r="I148" s="9"/>
@@ -7454,25 +7549,25 @@
     </x:row>
     <x:row r="149" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A149" s="12" t="s">
-        <x:v>563</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B149" s="12" t="s">
-        <x:v>550</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="C149" s="12" t="s">
-        <x:v>594</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="D149" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E149" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F149" s="12" t="s">
-        <x:v>759</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="G149" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="H149" s="9"/>
       <x:c r="I149" s="9"/>
@@ -7483,25 +7578,25 @@
     </x:row>
     <x:row r="150" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A150" s="12" t="s">
-        <x:v>544</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B150" s="12" t="s">
-        <x:v>574</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="C150" s="12" t="s">
-        <x:v>611</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="D150" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E150" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F150" s="12" t="s">
-        <x:v>740</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="G150" s="12" t="s">
-        <x:v>31</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H150" s="9"/>
       <x:c r="I150" s="9"/>
@@ -7512,25 +7607,25 @@
     </x:row>
     <x:row r="151" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A151" s="12" t="s">
-        <x:v>564</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B151" s="12" t="s">
-        <x:v>256</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="C151" s="12" t="s">
-        <x:v>641</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="D151" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E151" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F151" s="12" t="s">
-        <x:v>760</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="G151" s="12" t="s">
-        <x:v>6</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H151" s="9"/>
       <x:c r="I151" s="9"/>
@@ -7541,25 +7636,25 @@
     </x:row>
     <x:row r="152" spans="1:13" s="11" customFormat="1" customHeight="1">
       <x:c r="A152" s="12" t="s">
-        <x:v>560</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B152" s="12" t="s">
-        <x:v>262</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="C152" s="12" t="s">
-        <x:v>755</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="D152" s="12" t="s">
-        <x:v>280</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E152" s="12" t="s">
-        <x:v>556</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F152" s="12" t="s">
-        <x:v>745</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="G152" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H152" s="9"/>
       <x:c r="I152" s="9"/>
@@ -7568,7 +7663,28 @@
       <x:c r="L152" s="9"/>
       <x:c r="M152" s="9"/>
     </x:row>
-    <x:row r="153" spans="8:13" s="11" customFormat="1" customHeight="1">
+    <x:row r="153" spans="1:13" s="11" customFormat="1" customHeight="1">
+      <x:c r="A153" s="12" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B153" s="12" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C153" s="12" t="s">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="D153" s="12" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E153" s="12" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="F153" s="12" t="s">
+        <x:v>724</x:v>
+      </x:c>
+      <x:c r="G153" s="12" t="s">
+        <x:v>146</x:v>
+      </x:c>
       <x:c r="H153" s="9"/>
       <x:c r="I153" s="9"/>
       <x:c r="J153" s="9"/>
@@ -7576,6 +7692,135 @@
       <x:c r="L153" s="9"/>
       <x:c r="M153" s="9"/>
     </x:row>
+    <x:row r="154" spans="1:13" s="11" customFormat="1" customHeight="1">
+      <x:c r="A154" s="12" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B154" s="12" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="C154" s="12" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="D154" s="12" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E154" s="12" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="F154" s="12" t="s">
+        <x:v>776</x:v>
+      </x:c>
+      <x:c r="G154" s="12" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H154" s="9"/>
+      <x:c r="I154" s="9"/>
+      <x:c r="J154" s="9"/>
+      <x:c r="K154" s="9"/>
+      <x:c r="L154" s="9"/>
+      <x:c r="M154" s="9"/>
+    </x:row>
+    <x:row r="155" spans="1:13" s="11" customFormat="1" customHeight="1">
+      <x:c r="A155" s="12" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="B155" s="12" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="C155" s="12" t="s">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="D155" s="12" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E155" s="12" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="F155" s="12" t="s">
+        <x:v>752</x:v>
+      </x:c>
+      <x:c r="G155" s="12" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H155" s="9"/>
+      <x:c r="I155" s="9"/>
+      <x:c r="J155" s="9"/>
+      <x:c r="K155" s="9"/>
+      <x:c r="L155" s="9"/>
+      <x:c r="M155" s="9"/>
+    </x:row>
+    <x:row r="156" spans="1:13" s="11" customFormat="1" customHeight="1">
+      <x:c r="A156" s="12" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B156" s="12" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="C156" s="12" t="s">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="D156" s="12" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E156" s="12" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="F156" s="12" t="s">
+        <x:v>782</x:v>
+      </x:c>
+      <x:c r="G156" s="12" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H156" s="9"/>
+      <x:c r="I156" s="9"/>
+      <x:c r="J156" s="9"/>
+      <x:c r="K156" s="9"/>
+      <x:c r="L156" s="9"/>
+      <x:c r="M156" s="9"/>
+    </x:row>
+    <x:row r="157" spans="1:13" s="11" customFormat="1" customHeight="1">
+      <x:c r="A157" s="12" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B157" s="12" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="C157" s="12" t="s">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c r="D157" s="12" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="E157" s="12" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="F157" s="12" t="s">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="G157" s="12" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H157" s="9"/>
+      <x:c r="I157" s="9"/>
+      <x:c r="J157" s="9"/>
+      <x:c r="K157" s="9"/>
+      <x:c r="L157" s="9"/>
+      <x:c r="M157" s="9"/>
+    </x:row>
+    <x:row r="158" spans="1:13" s="11" customFormat="1" customHeight="1">
+      <x:c r="A158" s="22"/>
+      <x:c r="B158" s="22"/>
+      <x:c r="C158" s="22"/>
+      <x:c r="D158" s="22"/>
+      <x:c r="E158" s="22"/>
+      <x:c r="H158" s="9"/>
+      <x:c r="I158" s="9"/>
+      <x:c r="J158" s="9"/>
+      <x:c r="K158" s="9"/>
+      <x:c r="L158" s="9"/>
+      <x:c r="M158" s="9"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
